--- a/gabung.xlsx
+++ b/gabung.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="340">
   <si>
     <t>NAMA PEGAWAI</t>
   </si>
@@ -58,12 +58,6 @@
     <t>JUMLAH_ANAK</t>
   </si>
   <si>
-    <t>JABATAN</t>
-  </si>
-  <si>
-    <t>BESARAN_TPP</t>
-  </si>
-  <si>
     <t>BEBAN_KERJA</t>
   </si>
   <si>
@@ -785,9 +779,6 @@
   </si>
   <si>
     <t>K/2</t>
-  </si>
-  <si>
-    <t>Bendahara</t>
   </si>
   <si>
     <t>1904010504720002</t>
@@ -1400,10 +1391,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH42"/>
+  <dimension ref="A1:AF42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1500,22 +1491,16 @@
       <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:32">
+      <c r="A2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34">
-      <c r="A2" t="s">
-        <v>34</v>
-      </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D2">
         <v>9</v>
@@ -1530,96 +1515,90 @@
         <v>1626000</v>
       </c>
       <c r="H2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M2">
         <v>5452600</v>
       </c>
       <c r="N2" t="s">
-        <v>253</v>
-      </c>
-      <c r="O2" t="s">
-        <v>80</v>
+        <v>251</v>
+      </c>
+      <c r="O2">
+        <v>666660</v>
       </c>
       <c r="P2">
-        <v>1626000</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>666660</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>959340</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>959340</v>
+      <c r="T2" t="s">
+        <v>255</v>
       </c>
       <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2" t="s">
-        <v>258</v>
-      </c>
-      <c r="W2">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>73</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="Y2" t="s">
-        <v>75</v>
+        <v>297</v>
       </c>
       <c r="Z2">
-        <v>24</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
       </c>
       <c r="AB2">
         <v>1</v>
       </c>
-      <c r="AC2">
-        <v>1</v>
+      <c r="AC2" t="s">
+        <v>338</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>1610102532</v>
       </c>
       <c r="AE2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF2">
-        <v>1610102532</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH2">
         <v>83635</v>
       </c>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D3">
         <v>8</v>
@@ -1628,99 +1607,93 @@
         <v>1606000</v>
       </c>
       <c r="F3">
-        <v>92345</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1513655</v>
+        <v>1606000</v>
       </c>
       <c r="H3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M3">
         <v>3513600</v>
       </c>
       <c r="N3" t="s">
-        <v>254</v>
-      </c>
-      <c r="O3" t="s">
-        <v>81</v>
+        <v>252</v>
+      </c>
+      <c r="O3">
+        <v>835120</v>
       </c>
       <c r="P3">
-        <v>1606000</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>835120</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>770880</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>770880</v>
+      <c r="T3" t="s">
+        <v>256</v>
       </c>
       <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3" t="s">
-        <v>259</v>
-      </c>
-      <c r="W3">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="W3" t="s">
+        <v>74</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="s">
-        <v>76</v>
+        <v>298</v>
       </c>
       <c r="Z3">
-        <v>6</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>301</v>
+        <v>2</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>2</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>338</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>16109001439</v>
       </c>
       <c r="AE3" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF3">
-        <v>16109001439</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -1729,40 +1702,40 @@
         <v>1100000</v>
       </c>
       <c r="F4">
-        <v>3850</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1096150</v>
+        <v>1100000</v>
       </c>
       <c r="H4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M4">
         <v>4076400</v>
       </c>
       <c r="N4" t="s">
-        <v>255</v>
-      </c>
-      <c r="O4" t="s">
-        <v>82</v>
+        <v>253</v>
+      </c>
+      <c r="O4">
+        <v>1100000</v>
       </c>
       <c r="P4">
-        <v>1100000</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>1100000</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1770,17 +1743,17 @@
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
+      <c r="T4" t="s">
+        <v>257</v>
       </c>
       <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4" t="s">
-        <v>260</v>
-      </c>
-      <c r="W4">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V4">
+        <v>2</v>
+      </c>
+      <c r="W4" t="s">
+        <v>296</v>
       </c>
       <c r="X4">
         <v>2</v>
@@ -1789,39 +1762,33 @@
         <v>299</v>
       </c>
       <c r="Z4">
-        <v>2</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>302</v>
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
       </c>
       <c r="AB4">
-        <v>1</v>
-      </c>
-      <c r="AC4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>338</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1610800075</v>
       </c>
       <c r="AE4" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF4">
-        <v>1610800075</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -1830,40 +1797,40 @@
         <v>1000000</v>
       </c>
       <c r="F5">
-        <v>144000</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>856000</v>
+        <v>1000000</v>
       </c>
       <c r="H5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M5">
         <v>3961800</v>
       </c>
       <c r="N5" t="s">
-        <v>255</v>
-      </c>
-      <c r="O5" t="s">
-        <v>82</v>
+        <v>253</v>
+      </c>
+      <c r="O5">
+        <v>1000000</v>
       </c>
       <c r="P5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1871,58 +1838,52 @@
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
+      <c r="T5" t="s">
+        <v>258</v>
       </c>
       <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5" t="s">
-        <v>261</v>
-      </c>
-      <c r="W5">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V5">
+        <v>2</v>
+      </c>
+      <c r="W5" t="s">
+        <v>296</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>303</v>
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
       </c>
       <c r="AB5">
-        <v>1</v>
-      </c>
-      <c r="AC5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>338</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1440966672</v>
       </c>
       <c r="AE5" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF5">
-        <v>1440966672</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -1931,99 +1892,93 @@
         <v>1606000</v>
       </c>
       <c r="F6">
-        <v>5621</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>1600379</v>
+        <v>1606000</v>
       </c>
       <c r="H6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M6">
         <v>3959700</v>
       </c>
       <c r="N6" t="s">
-        <v>256</v>
-      </c>
-      <c r="O6" t="s">
-        <v>81</v>
+        <v>254</v>
+      </c>
+      <c r="O6">
+        <v>835120</v>
       </c>
       <c r="P6">
-        <v>1606000</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>835120</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>770880</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>770880</v>
+      <c r="T6" t="s">
+        <v>259</v>
       </c>
       <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6" t="s">
-        <v>262</v>
-      </c>
-      <c r="W6">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6" t="s">
+        <v>74</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="s">
-        <v>76</v>
+        <v>301</v>
       </c>
       <c r="Z6">
-        <v>6</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>304</v>
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
       </c>
       <c r="AB6">
-        <v>1</v>
-      </c>
-      <c r="AC6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>338</v>
       </c>
       <c r="AD6">
-        <v>2</v>
+        <v>15509001575</v>
       </c>
       <c r="AE6" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF6">
-        <v>15509001575</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -2032,40 +1987,40 @@
         <v>1000000</v>
       </c>
       <c r="F7">
-        <v>94500</v>
+        <v>36500</v>
       </c>
       <c r="G7">
-        <v>905500</v>
+        <v>963500</v>
       </c>
       <c r="H7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M7">
         <v>4144500</v>
       </c>
       <c r="N7" t="s">
-        <v>253</v>
-      </c>
-      <c r="O7" t="s">
-        <v>82</v>
+        <v>251</v>
+      </c>
+      <c r="O7">
+        <v>963500</v>
       </c>
       <c r="P7">
-        <v>996500</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>996500</v>
+        <v>0</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2073,58 +2028,52 @@
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
+      <c r="T7" t="s">
+        <v>260</v>
       </c>
       <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7" t="s">
-        <v>263</v>
-      </c>
-      <c r="W7">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V7">
+        <v>2</v>
+      </c>
+      <c r="W7" t="s">
+        <v>296</v>
       </c>
       <c r="X7">
         <v>2</v>
       </c>
       <c r="Y7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Z7">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>305</v>
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
       </c>
       <c r="AB7">
         <v>1</v>
       </c>
-      <c r="AC7">
-        <v>1</v>
+      <c r="AC7" t="s">
+        <v>338</v>
       </c>
       <c r="AD7">
-        <v>1</v>
+        <v>1610905992</v>
       </c>
       <c r="AE7" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF7">
-        <v>1610905992</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -2133,102 +2082,96 @@
         <v>1626000</v>
       </c>
       <c r="F8">
-        <v>110568</v>
+        <v>17073</v>
       </c>
       <c r="G8">
-        <v>1515432</v>
+        <v>1608927</v>
       </c>
       <c r="H8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M8">
         <v>4658300</v>
       </c>
       <c r="N8" t="s">
-        <v>256</v>
-      </c>
-      <c r="O8" t="s">
-        <v>80</v>
+        <v>254</v>
+      </c>
+      <c r="O8">
+        <v>659660</v>
       </c>
       <c r="P8">
-        <v>1626000</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>666660</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>949267</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>959340</v>
+      <c r="T8" t="s">
+        <v>261</v>
       </c>
       <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8" t="s">
-        <v>264</v>
-      </c>
-      <c r="W8">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8" t="s">
+        <v>73</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y8" t="s">
-        <v>75</v>
+        <v>303</v>
       </c>
       <c r="Z8">
-        <v>10</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>306</v>
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
       </c>
       <c r="AB8">
-        <v>1</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>338</v>
       </c>
       <c r="AD8">
-        <v>2</v>
+        <v>1610905249</v>
       </c>
       <c r="AE8" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF8">
-        <v>1610905249</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH8">
         <v>66618</v>
       </c>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D9">
         <v>9</v>
@@ -2243,96 +2186,90 @@
         <v>1620309</v>
       </c>
       <c r="H9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M9">
         <v>5080700</v>
       </c>
       <c r="N9" t="s">
-        <v>256</v>
-      </c>
-      <c r="O9" t="s">
-        <v>80</v>
+        <v>254</v>
+      </c>
+      <c r="O9">
+        <v>664327</v>
       </c>
       <c r="P9">
-        <v>1614618</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>661993</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>955982</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>952625</v>
+      <c r="T9" t="s">
+        <v>262</v>
       </c>
       <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9" t="s">
-        <v>265</v>
-      </c>
-      <c r="W9">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9" t="s">
+        <v>73</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="s">
-        <v>75</v>
+        <v>304</v>
       </c>
       <c r="Z9">
-        <v>16</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>307</v>
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
       </c>
       <c r="AB9">
-        <v>1</v>
-      </c>
-      <c r="AC9">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>338</v>
       </c>
       <c r="AD9">
-        <v>2</v>
+        <v>1610105556</v>
       </c>
       <c r="AE9" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF9">
-        <v>1610105556</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH9">
         <v>76207</v>
       </c>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -2347,96 +2284,90 @@
         <v>1626000</v>
       </c>
       <c r="H10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M10">
         <v>4658300</v>
       </c>
       <c r="N10" t="s">
-        <v>256</v>
-      </c>
-      <c r="O10" t="s">
-        <v>80</v>
+        <v>254</v>
+      </c>
+      <c r="O10">
+        <v>666660</v>
       </c>
       <c r="P10">
-        <v>1626000</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>666660</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>959340</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>959340</v>
+      <c r="T10" t="s">
+        <v>263</v>
       </c>
       <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10" t="s">
-        <v>266</v>
-      </c>
-      <c r="W10">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10" t="s">
+        <v>73</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="s">
-        <v>75</v>
+        <v>305</v>
       </c>
       <c r="Z10">
-        <v>12</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>308</v>
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
       </c>
       <c r="AB10">
-        <v>1</v>
-      </c>
-      <c r="AC10">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>338</v>
       </c>
       <c r="AD10">
-        <v>2</v>
+        <v>1610107829</v>
       </c>
       <c r="AE10" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF10">
-        <v>1610107829</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH10">
         <v>67405</v>
       </c>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D11">
         <v>11</v>
@@ -2445,102 +2376,96 @@
         <v>1842000</v>
       </c>
       <c r="F11">
-        <v>194331</v>
+        <v>128019</v>
       </c>
       <c r="G11">
-        <v>1647669</v>
+        <v>1713981</v>
       </c>
       <c r="H11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M11">
         <v>5343700</v>
       </c>
       <c r="N11" t="s">
-        <v>256</v>
-      </c>
-      <c r="O11" t="s">
-        <v>83</v>
+        <v>254</v>
+      </c>
+      <c r="O11">
+        <v>531334</v>
       </c>
       <c r="P11">
-        <v>1814370</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>562455</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1182647</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>1251915</v>
+      <c r="T11" t="s">
+        <v>264</v>
       </c>
       <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11" t="s">
-        <v>267</v>
-      </c>
-      <c r="W11">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11" t="s">
+        <v>76</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="s">
+        <v>306</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD11">
+        <v>1610906028</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>339</v>
+      </c>
+      <c r="AF11">
+        <v>76207</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
         <v>78</v>
-      </c>
-      <c r="Z11">
-        <v>17</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>309</v>
-      </c>
-      <c r="AB11">
-        <v>1</v>
-      </c>
-      <c r="AC11">
-        <v>1</v>
-      </c>
-      <c r="AD11">
-        <v>2</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF11">
-        <v>1610906028</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH11">
-        <v>76207</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34">
-      <c r="A12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>80</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -2549,102 +2474,96 @@
         <v>1626000</v>
       </c>
       <c r="F12">
-        <v>58536</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>1567464</v>
+        <v>1626000</v>
       </c>
       <c r="H12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M12">
         <v>4716400</v>
       </c>
       <c r="N12" t="s">
-        <v>253</v>
-      </c>
-      <c r="O12" t="s">
-        <v>80</v>
+        <v>251</v>
+      </c>
+      <c r="O12">
+        <v>666660</v>
       </c>
       <c r="P12">
-        <v>1620309</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>664327</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>959340</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>955982</v>
+      <c r="T12" t="s">
+        <v>265</v>
       </c>
       <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12" t="s">
-        <v>268</v>
-      </c>
-      <c r="W12">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12" t="s">
+        <v>73</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="s">
-        <v>75</v>
+        <v>307</v>
       </c>
       <c r="Z12">
-        <v>14</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>310</v>
+        <v>1</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
       </c>
       <c r="AB12">
         <v>1</v>
       </c>
-      <c r="AC12">
-        <v>1</v>
+      <c r="AC12" t="s">
+        <v>338</v>
       </c>
       <c r="AD12">
-        <v>1</v>
+        <v>1610106971</v>
       </c>
       <c r="AE12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF12">
-        <v>1610106971</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH12">
         <v>68716</v>
       </c>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D13">
         <v>11</v>
@@ -2659,96 +2578,90 @@
         <v>1842000</v>
       </c>
       <c r="H13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M13">
         <v>5343700</v>
       </c>
       <c r="N13" t="s">
-        <v>256</v>
-      </c>
-      <c r="O13" t="s">
-        <v>83</v>
+        <v>254</v>
+      </c>
+      <c r="O13">
+        <v>571020</v>
       </c>
       <c r="P13">
-        <v>1835553</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>569021</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1270980</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>1266532</v>
+      <c r="T13" t="s">
+        <v>266</v>
       </c>
       <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13" t="s">
-        <v>269</v>
-      </c>
-      <c r="W13">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13" t="s">
+        <v>76</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Y13" t="s">
-        <v>78</v>
+        <v>308</v>
       </c>
       <c r="Z13">
-        <v>17</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>311</v>
+        <v>1</v>
+      </c>
+      <c r="AA13">
+        <v>1</v>
       </c>
       <c r="AB13">
-        <v>1</v>
-      </c>
-      <c r="AC13">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>338</v>
       </c>
       <c r="AD13">
-        <v>2</v>
+        <v>1610106580</v>
       </c>
       <c r="AE13" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF13">
-        <v>1610106580</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH13">
         <v>76207</v>
       </c>
     </row>
-    <row r="14" spans="1:34">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D14">
         <v>8</v>
@@ -2763,93 +2676,87 @@
         <v>4743000</v>
       </c>
       <c r="H14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K14" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L14" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="M14">
         <v>5821400</v>
       </c>
       <c r="N14" t="s">
-        <v>256</v>
-      </c>
-      <c r="O14" t="s">
-        <v>84</v>
+        <v>254</v>
+      </c>
+      <c r="O14">
+        <v>3984120</v>
       </c>
       <c r="P14">
-        <v>4743000</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>3984120</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>758880</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>758880</v>
+      <c r="T14" t="s">
+        <v>267</v>
       </c>
       <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14" t="s">
-        <v>270</v>
-      </c>
-      <c r="W14">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14" t="s">
+        <v>73</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="s">
-        <v>75</v>
+        <v>309</v>
       </c>
       <c r="Z14">
-        <v>18</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>312</v>
+        <v>1</v>
+      </c>
+      <c r="AA14">
+        <v>1</v>
       </c>
       <c r="AB14">
-        <v>1</v>
-      </c>
-      <c r="AC14">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>338</v>
       </c>
       <c r="AD14">
-        <v>2</v>
+        <v>1440105481</v>
       </c>
       <c r="AE14" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF14">
-        <v>1440105481</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -2858,99 +2765,93 @@
         <v>1606000</v>
       </c>
       <c r="F15">
-        <v>57816</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>1548184</v>
+        <v>1606000</v>
       </c>
       <c r="H15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L15" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M15">
         <v>3934500</v>
       </c>
       <c r="N15" t="s">
-        <v>254</v>
-      </c>
-      <c r="O15" t="s">
-        <v>81</v>
+        <v>252</v>
+      </c>
+      <c r="O15">
+        <v>835120</v>
       </c>
       <c r="P15">
-        <v>1606000</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>835120</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>770880</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>770880</v>
+      <c r="T15" t="s">
+        <v>268</v>
       </c>
       <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15" t="s">
-        <v>271</v>
-      </c>
-      <c r="W15">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15" t="s">
+        <v>74</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="s">
-        <v>76</v>
+        <v>310</v>
       </c>
       <c r="Z15">
-        <v>14</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>313</v>
+        <v>2</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>2</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>338</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1460107125</v>
       </c>
       <c r="AE15" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF15">
-        <v>1460107125</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="16" spans="1:34">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -2959,40 +2860,40 @@
         <v>1000000</v>
       </c>
       <c r="F16">
-        <v>718000</v>
+        <v>700000</v>
       </c>
       <c r="G16">
-        <v>282000</v>
+        <v>300000</v>
       </c>
       <c r="H16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J16" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K16" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M16">
         <v>3631400</v>
       </c>
       <c r="N16" t="s">
-        <v>254</v>
-      </c>
-      <c r="O16" t="s">
-        <v>82</v>
+        <v>252</v>
+      </c>
+      <c r="O16">
+        <v>300000</v>
       </c>
       <c r="P16">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -3000,58 +2901,52 @@
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16">
-        <v>0</v>
+      <c r="T16" t="s">
+        <v>269</v>
       </c>
       <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16" t="s">
-        <v>272</v>
-      </c>
-      <c r="W16">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V16">
+        <v>2</v>
+      </c>
+      <c r="W16" t="s">
+        <v>296</v>
       </c>
       <c r="X16">
         <v>2</v>
       </c>
       <c r="Y16" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="Z16">
         <v>2</v>
       </c>
-      <c r="AA16" t="s">
-        <v>314</v>
+      <c r="AA16">
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>2</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>338</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>16109000456</v>
       </c>
       <c r="AE16" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF16">
-        <v>16109000456</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="17" spans="1:34">
+    <row r="17" spans="1:32">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D17">
         <v>11</v>
@@ -3060,102 +2955,96 @@
         <v>1842000</v>
       </c>
       <c r="F17">
-        <v>6447</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>1835553</v>
+        <v>1842000</v>
       </c>
       <c r="H17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J17" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K17" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M17">
         <v>5499700</v>
       </c>
       <c r="N17" t="s">
-        <v>256</v>
-      </c>
-      <c r="O17" t="s">
-        <v>83</v>
+        <v>254</v>
+      </c>
+      <c r="O17">
+        <v>571020</v>
       </c>
       <c r="P17">
-        <v>1842000</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>571020</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1270980</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
-      <c r="T17">
-        <v>1270980</v>
+      <c r="T17" t="s">
+        <v>270</v>
       </c>
       <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17" t="s">
-        <v>273</v>
-      </c>
-      <c r="W17">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17" t="s">
+        <v>76</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="s">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="Z17">
-        <v>20</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>315</v>
+        <v>1</v>
+      </c>
+      <c r="AA17">
+        <v>1</v>
       </c>
       <c r="AB17">
-        <v>1</v>
-      </c>
-      <c r="AC17">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>338</v>
       </c>
       <c r="AD17">
-        <v>2</v>
+        <v>1900900969</v>
       </c>
       <c r="AE17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF17">
-        <v>1900900969</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH17">
         <v>78605</v>
       </c>
     </row>
-    <row r="18" spans="1:34">
+    <row r="18" spans="1:32">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D18">
         <v>8</v>
@@ -3164,40 +3053,40 @@
         <v>1000000</v>
       </c>
       <c r="F18">
-        <v>111500</v>
+        <v>18000</v>
       </c>
       <c r="G18">
-        <v>888500</v>
+        <v>982000</v>
       </c>
       <c r="H18" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J18" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L18" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M18">
         <v>4212700</v>
       </c>
       <c r="N18" t="s">
-        <v>256</v>
-      </c>
-      <c r="O18" t="s">
-        <v>82</v>
+        <v>254</v>
+      </c>
+      <c r="O18">
+        <v>982000</v>
       </c>
       <c r="P18">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -3205,58 +3094,52 @@
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>0</v>
+      <c r="T18" t="s">
+        <v>271</v>
       </c>
       <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18" t="s">
-        <v>274</v>
-      </c>
-      <c r="W18">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V18">
+        <v>2</v>
+      </c>
+      <c r="W18" t="s">
+        <v>296</v>
       </c>
       <c r="X18">
         <v>2</v>
       </c>
       <c r="Y18" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="Z18">
-        <v>2</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>316</v>
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
       </c>
       <c r="AB18">
-        <v>1</v>
-      </c>
-      <c r="AC18">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>338</v>
       </c>
       <c r="AD18">
-        <v>2</v>
+        <v>1610906064</v>
       </c>
       <c r="AE18" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF18">
-        <v>1610906064</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:34">
+    <row r="19" spans="1:32">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D19">
         <v>8</v>
@@ -3265,40 +3148,40 @@
         <v>1000000</v>
       </c>
       <c r="F19">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>982000</v>
+        <v>1000000</v>
       </c>
       <c r="H19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I19" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J19" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K19" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L19" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M19">
         <v>3631400</v>
       </c>
       <c r="N19" t="s">
-        <v>254</v>
-      </c>
-      <c r="O19" t="s">
-        <v>82</v>
+        <v>252</v>
+      </c>
+      <c r="O19">
+        <v>1000000</v>
       </c>
       <c r="P19">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -3306,58 +3189,52 @@
       <c r="S19">
         <v>0</v>
       </c>
-      <c r="T19">
-        <v>0</v>
+      <c r="T19" t="s">
+        <v>272</v>
       </c>
       <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19" t="s">
-        <v>275</v>
-      </c>
-      <c r="W19">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V19">
+        <v>2</v>
+      </c>
+      <c r="W19" t="s">
+        <v>296</v>
       </c>
       <c r="X19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>317</v>
+        <v>2</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>2</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>338</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>16109000347</v>
       </c>
       <c r="AE19" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF19">
-        <v>16109000347</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="20" spans="1:34">
+    <row r="20" spans="1:32">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D20">
         <v>9</v>
@@ -3366,102 +3243,96 @@
         <v>1626000</v>
       </c>
       <c r="F20">
-        <v>99186</v>
+        <v>11382</v>
       </c>
       <c r="G20">
-        <v>1526814</v>
+        <v>1614618</v>
       </c>
       <c r="H20" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J20" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M20">
         <v>4773800</v>
       </c>
       <c r="N20" t="s">
-        <v>255</v>
-      </c>
-      <c r="O20" t="s">
-        <v>80</v>
+        <v>253</v>
+      </c>
+      <c r="O20">
+        <v>661993</v>
       </c>
       <c r="P20">
-        <v>1620309</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>664327</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>952625</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
-      <c r="T20">
-        <v>955982</v>
+      <c r="T20" t="s">
+        <v>273</v>
       </c>
       <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20" t="s">
-        <v>276</v>
-      </c>
-      <c r="W20">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20" t="s">
+        <v>73</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y20" t="s">
-        <v>75</v>
+        <v>315</v>
       </c>
       <c r="Z20">
-        <v>16</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>318</v>
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>1</v>
       </c>
       <c r="AB20">
-        <v>1</v>
-      </c>
-      <c r="AC20">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>338</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1610901678</v>
       </c>
       <c r="AE20" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF20">
-        <v>1610901678</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH20">
         <v>73880</v>
       </c>
     </row>
-    <row r="21" spans="1:34">
+    <row r="21" spans="1:32">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D21">
         <v>9</v>
@@ -3476,96 +3347,90 @@
         <v>1626000</v>
       </c>
       <c r="H21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J21" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K21" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L21" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M21">
         <v>4658300</v>
       </c>
       <c r="N21" t="s">
-        <v>256</v>
-      </c>
-      <c r="O21" t="s">
+        <v>254</v>
+      </c>
+      <c r="O21">
+        <v>666660</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>959340</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21" t="s">
+        <v>274</v>
+      </c>
+      <c r="U21">
+        <v>2</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21" t="s">
+        <v>73</v>
+      </c>
+      <c r="X21">
+        <v>12</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>316</v>
+      </c>
+      <c r="Z21">
+        <v>1</v>
+      </c>
+      <c r="AA21">
+        <v>1</v>
+      </c>
+      <c r="AB21">
+        <v>2</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD21">
+        <v>1610904070</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>339</v>
+      </c>
+      <c r="AF21">
+        <v>66618</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32">
+      <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s">
         <v>80</v>
-      </c>
-      <c r="P21">
-        <v>1626000</v>
-      </c>
-      <c r="Q21">
-        <v>666660</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>959340</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21" t="s">
-        <v>277</v>
-      </c>
-      <c r="W21">
-        <v>2</v>
-      </c>
-      <c r="X21">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z21">
-        <v>12</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>319</v>
-      </c>
-      <c r="AB21">
-        <v>1</v>
-      </c>
-      <c r="AC21">
-        <v>1</v>
-      </c>
-      <c r="AD21">
-        <v>2</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF21">
-        <v>1610904070</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH21">
-        <v>66618</v>
-      </c>
-    </row>
-    <row r="22" spans="1:34">
-      <c r="A22" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" t="s">
-        <v>82</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -3580,34 +3445,34 @@
         <v>996500</v>
       </c>
       <c r="H22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I22" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K22" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="L22" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M22">
         <v>3735500</v>
       </c>
       <c r="N22" t="s">
-        <v>254</v>
-      </c>
-      <c r="O22" t="s">
-        <v>82</v>
+        <v>252</v>
+      </c>
+      <c r="O22">
+        <v>996500</v>
       </c>
       <c r="P22">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -3615,58 +3480,52 @@
       <c r="S22">
         <v>0</v>
       </c>
-      <c r="T22">
-        <v>0</v>
+      <c r="T22" t="s">
+        <v>275</v>
       </c>
       <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22" t="s">
-        <v>278</v>
-      </c>
-      <c r="W22">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V22">
+        <v>2</v>
+      </c>
+      <c r="W22" t="s">
+        <v>296</v>
       </c>
       <c r="X22">
         <v>2</v>
       </c>
       <c r="Y22" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="Z22">
         <v>2</v>
       </c>
-      <c r="AA22" t="s">
-        <v>320</v>
+      <c r="AA22">
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>2</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>338</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1820903520</v>
       </c>
       <c r="AE22" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF22">
-        <v>1820903520</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="23" spans="1:34">
+    <row r="23" spans="1:32">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D23">
         <v>9</v>
@@ -3675,102 +3534,96 @@
         <v>1626000</v>
       </c>
       <c r="F23">
-        <v>34959</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>1591041</v>
+        <v>1626000</v>
       </c>
       <c r="H23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I23" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K23" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M23">
         <v>4496900</v>
       </c>
       <c r="N23" t="s">
-        <v>255</v>
-      </c>
-      <c r="O23" t="s">
-        <v>80</v>
+        <v>253</v>
+      </c>
+      <c r="O23">
+        <v>666660</v>
       </c>
       <c r="P23">
-        <v>1626000</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>666660</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>959340</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
-      <c r="T23">
-        <v>959340</v>
+      <c r="T23" t="s">
+        <v>276</v>
       </c>
       <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23" t="s">
-        <v>279</v>
-      </c>
-      <c r="W23">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23" t="s">
+        <v>73</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y23" t="s">
-        <v>75</v>
+        <v>318</v>
       </c>
       <c r="Z23">
-        <v>16</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>321</v>
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>1</v>
-      </c>
-      <c r="AC23">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>338</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1610105795</v>
       </c>
       <c r="AE23" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF23">
-        <v>1610105795</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH23">
         <v>76207</v>
       </c>
     </row>
-    <row r="24" spans="1:34">
+    <row r="24" spans="1:32">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D24">
         <v>9</v>
@@ -3785,96 +3638,90 @@
         <v>1620309</v>
       </c>
       <c r="H24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K24" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M24">
         <v>5614000</v>
       </c>
       <c r="N24" t="s">
-        <v>253</v>
-      </c>
-      <c r="O24" t="s">
-        <v>80</v>
+        <v>251</v>
+      </c>
+      <c r="O24">
+        <v>664327</v>
       </c>
       <c r="P24">
-        <v>1626000</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>666660</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>955982</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
-      <c r="T24">
-        <v>959340</v>
+      <c r="T24" t="s">
+        <v>277</v>
       </c>
       <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24" t="s">
-        <v>280</v>
-      </c>
-      <c r="W24">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24" t="s">
+        <v>73</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="Y24" t="s">
-        <v>75</v>
+        <v>319</v>
       </c>
       <c r="Z24">
-        <v>26</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>322</v>
+        <v>1</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
       </c>
       <c r="AB24">
         <v>1</v>
       </c>
-      <c r="AC24">
-        <v>1</v>
+      <c r="AC24" t="s">
+        <v>338</v>
       </c>
       <c r="AD24">
-        <v>1</v>
+        <v>1610101008</v>
       </c>
       <c r="AE24" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF24">
-        <v>1610101008</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH24">
         <v>86270</v>
       </c>
     </row>
-    <row r="25" spans="1:34">
+    <row r="25" spans="1:32">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D25">
         <v>9</v>
@@ -3889,96 +3736,90 @@
         <v>1626000</v>
       </c>
       <c r="H25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I25" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J25" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K25" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L25" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M25">
         <v>4506300</v>
       </c>
       <c r="N25" t="s">
-        <v>255</v>
-      </c>
-      <c r="O25" t="s">
-        <v>80</v>
+        <v>253</v>
+      </c>
+      <c r="O25">
+        <v>666660</v>
       </c>
       <c r="P25">
-        <v>1626000</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>666660</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>959340</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
-      <c r="T25">
-        <v>959340</v>
+      <c r="T25" t="s">
+        <v>278</v>
       </c>
       <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25" t="s">
-        <v>281</v>
-      </c>
-      <c r="W25">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
+      </c>
+      <c r="W25" t="s">
+        <v>73</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y25" t="s">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="Z25">
-        <v>10</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>323</v>
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>1</v>
       </c>
       <c r="AB25">
-        <v>1</v>
-      </c>
-      <c r="AC25">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>338</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1610905245</v>
       </c>
       <c r="AE25" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF25">
-        <v>1610905245</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH25">
         <v>66618</v>
       </c>
     </row>
-    <row r="26" spans="1:34">
+    <row r="26" spans="1:32">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D26">
         <v>9</v>
@@ -3987,102 +3828,96 @@
         <v>1626000</v>
       </c>
       <c r="F26">
-        <v>204876</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>1421124</v>
+        <v>1626000</v>
       </c>
       <c r="H26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I26" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J26" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K26" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L26" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M26">
         <v>4935500</v>
       </c>
       <c r="N26" t="s">
-        <v>256</v>
-      </c>
-      <c r="O26" t="s">
-        <v>80</v>
+        <v>254</v>
+      </c>
+      <c r="O26">
+        <v>666660</v>
       </c>
       <c r="P26">
-        <v>1620309</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>664327</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>959340</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
-      <c r="T26">
-        <v>955982</v>
+      <c r="T26" t="s">
+        <v>279</v>
       </c>
       <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26" t="s">
-        <v>282</v>
-      </c>
-      <c r="W26">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V26">
+        <v>1</v>
+      </c>
+      <c r="W26" t="s">
+        <v>73</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y26" t="s">
-        <v>75</v>
+        <v>321</v>
       </c>
       <c r="Z26">
-        <v>16</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>324</v>
+        <v>1</v>
+      </c>
+      <c r="AA26">
+        <v>1</v>
       </c>
       <c r="AB26">
-        <v>1</v>
-      </c>
-      <c r="AC26">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>338</v>
       </c>
       <c r="AD26">
-        <v>2</v>
+        <v>1610104975</v>
       </c>
       <c r="AE26" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF26">
-        <v>1610104975</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH26">
         <v>73880</v>
       </c>
     </row>
-    <row r="27" spans="1:34">
+    <row r="27" spans="1:32">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D27">
         <v>7</v>
@@ -4091,99 +3926,93 @@
         <v>2667000</v>
       </c>
       <c r="F27">
-        <v>216027</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>2450973</v>
+        <v>2667000</v>
       </c>
       <c r="H27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I27" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J27" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K27" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L27" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M27">
         <v>4352600</v>
       </c>
       <c r="N27" t="s">
-        <v>253</v>
-      </c>
-      <c r="O27" t="s">
-        <v>257</v>
+        <v>251</v>
+      </c>
+      <c r="O27">
+        <v>1973580</v>
       </c>
       <c r="P27">
-        <v>2667000</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>1973580</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>693420</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
-      <c r="T27">
-        <v>693420</v>
+      <c r="T27" t="s">
+        <v>280</v>
       </c>
       <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27" t="s">
-        <v>283</v>
-      </c>
-      <c r="W27">
         <v>3</v>
       </c>
+      <c r="V27">
+        <v>1</v>
+      </c>
+      <c r="W27" t="s">
+        <v>296</v>
+      </c>
       <c r="X27">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y27" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="Z27">
-        <v>16</v>
-      </c>
-      <c r="AA27" t="s">
-        <v>325</v>
+        <v>1</v>
+      </c>
+      <c r="AA27">
+        <v>1</v>
       </c>
       <c r="AB27">
         <v>1</v>
       </c>
-      <c r="AC27">
-        <v>1</v>
+      <c r="AC27" t="s">
+        <v>338</v>
       </c>
       <c r="AD27">
-        <v>1</v>
+        <v>1610103820</v>
       </c>
       <c r="AE27" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF27">
-        <v>1610103820</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="28" spans="1:34">
+    <row r="28" spans="1:32">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D28">
         <v>8</v>
@@ -4198,34 +4027,34 @@
         <v>1000000</v>
       </c>
       <c r="H28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I28" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J28" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L28" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M28">
         <v>4094000</v>
       </c>
       <c r="N28" t="s">
-        <v>256</v>
-      </c>
-      <c r="O28" t="s">
-        <v>82</v>
+        <v>254</v>
+      </c>
+      <c r="O28">
+        <v>1000000</v>
       </c>
       <c r="P28">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -4233,58 +4062,52 @@
       <c r="S28">
         <v>0</v>
       </c>
-      <c r="T28">
-        <v>0</v>
+      <c r="T28" t="s">
+        <v>281</v>
       </c>
       <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28" t="s">
-        <v>284</v>
-      </c>
-      <c r="W28">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V28">
+        <v>2</v>
+      </c>
+      <c r="W28" t="s">
+        <v>296</v>
       </c>
       <c r="X28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>326</v>
+        <v>1</v>
+      </c>
+      <c r="AA28">
+        <v>1</v>
       </c>
       <c r="AB28">
-        <v>1</v>
-      </c>
-      <c r="AC28">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>338</v>
       </c>
       <c r="AD28">
-        <v>2</v>
+        <v>1610907514</v>
       </c>
       <c r="AE28" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF28">
-        <v>1610907514</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="29" spans="1:34">
+    <row r="29" spans="1:32">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D29">
         <v>8</v>
@@ -4293,40 +4116,40 @@
         <v>1000000</v>
       </c>
       <c r="F29">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>982000</v>
+        <v>1000000</v>
       </c>
       <c r="H29" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I29" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J29" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K29" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L29" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M29">
         <v>3961800</v>
       </c>
       <c r="N29" t="s">
-        <v>255</v>
-      </c>
-      <c r="O29" t="s">
-        <v>82</v>
+        <v>253</v>
+      </c>
+      <c r="O29">
+        <v>1000000</v>
       </c>
       <c r="P29">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -4334,58 +4157,52 @@
       <c r="S29">
         <v>0</v>
       </c>
-      <c r="T29">
-        <v>0</v>
+      <c r="T29" t="s">
+        <v>282</v>
       </c>
       <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29" t="s">
-        <v>285</v>
-      </c>
-      <c r="W29">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V29">
+        <v>2</v>
+      </c>
+      <c r="W29" t="s">
+        <v>296</v>
       </c>
       <c r="X29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>327</v>
+        <v>2</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>2</v>
-      </c>
-      <c r="AC29">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>338</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1440966655</v>
       </c>
       <c r="AE29" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF29">
-        <v>1440966655</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="30" spans="1:34">
+    <row r="30" spans="1:32">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D30">
         <v>9</v>
@@ -4394,102 +4211,96 @@
         <v>1626000</v>
       </c>
       <c r="F30">
-        <v>93495</v>
+        <v>5691</v>
       </c>
       <c r="G30">
-        <v>1532505</v>
+        <v>1620309</v>
       </c>
       <c r="H30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I30" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J30" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K30" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L30" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M30">
         <v>4935500</v>
       </c>
       <c r="N30" t="s">
-        <v>256</v>
-      </c>
-      <c r="O30" t="s">
-        <v>80</v>
+        <v>254</v>
+      </c>
+      <c r="O30">
+        <v>664327</v>
       </c>
       <c r="P30">
-        <v>1626000</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>666660</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>955982</v>
       </c>
       <c r="S30">
         <v>0</v>
       </c>
-      <c r="T30">
-        <v>959340</v>
+      <c r="T30" t="s">
+        <v>283</v>
       </c>
       <c r="U30">
-        <v>0</v>
-      </c>
-      <c r="V30" t="s">
-        <v>286</v>
-      </c>
-      <c r="W30">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V30">
+        <v>1</v>
+      </c>
+      <c r="W30" t="s">
+        <v>73</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y30" t="s">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="Z30">
-        <v>16</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>328</v>
+        <v>1</v>
+      </c>
+      <c r="AA30">
+        <v>1</v>
       </c>
       <c r="AB30">
-        <v>1</v>
-      </c>
-      <c r="AC30">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>338</v>
       </c>
       <c r="AD30">
-        <v>2</v>
+        <v>1610106127</v>
       </c>
       <c r="AE30" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF30">
-        <v>1610106127</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH30">
         <v>73880</v>
       </c>
     </row>
-    <row r="31" spans="1:34">
+    <row r="31" spans="1:32">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D31">
         <v>9</v>
@@ -4504,96 +4315,90 @@
         <v>1626000</v>
       </c>
       <c r="H31" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I31" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K31" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L31" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M31">
         <v>4935500</v>
       </c>
       <c r="N31" t="s">
-        <v>256</v>
-      </c>
-      <c r="O31" t="s">
+        <v>254</v>
+      </c>
+      <c r="O31">
+        <v>666660</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>959340</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31" t="s">
+        <v>284</v>
+      </c>
+      <c r="U31">
+        <v>2</v>
+      </c>
+      <c r="V31">
+        <v>1</v>
+      </c>
+      <c r="W31" t="s">
+        <v>73</v>
+      </c>
+      <c r="X31">
+        <v>16</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>326</v>
+      </c>
+      <c r="Z31">
+        <v>1</v>
+      </c>
+      <c r="AA31">
+        <v>1</v>
+      </c>
+      <c r="AB31">
+        <v>2</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD31">
+        <v>1610100879</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>339</v>
+      </c>
+      <c r="AF31">
+        <v>73880</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" t="s">
         <v>80</v>
-      </c>
-      <c r="P31">
-        <v>1626000</v>
-      </c>
-      <c r="Q31">
-        <v>666660</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>959340</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31" t="s">
-        <v>287</v>
-      </c>
-      <c r="W31">
-        <v>2</v>
-      </c>
-      <c r="X31">
-        <v>1</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z31">
-        <v>16</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>329</v>
-      </c>
-      <c r="AB31">
-        <v>1</v>
-      </c>
-      <c r="AC31">
-        <v>1</v>
-      </c>
-      <c r="AD31">
-        <v>2</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF31">
-        <v>1610100879</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH31">
-        <v>73880</v>
-      </c>
-    </row>
-    <row r="32" spans="1:34">
-      <c r="A32" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" t="s">
-        <v>82</v>
       </c>
       <c r="D32">
         <v>8</v>
@@ -4602,40 +4407,40 @@
         <v>1000000</v>
       </c>
       <c r="F32">
-        <v>75500</v>
+        <v>3500</v>
       </c>
       <c r="G32">
-        <v>924500</v>
+        <v>996500</v>
       </c>
       <c r="H32" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I32" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J32" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K32" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L32" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M32">
         <v>3631400</v>
       </c>
       <c r="N32" t="s">
-        <v>255</v>
-      </c>
-      <c r="O32" t="s">
-        <v>82</v>
+        <v>253</v>
+      </c>
+      <c r="O32">
+        <v>996500</v>
       </c>
       <c r="P32">
-        <v>996500</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>996500</v>
+        <v>0</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -4643,58 +4448,52 @@
       <c r="S32">
         <v>0</v>
       </c>
-      <c r="T32">
-        <v>0</v>
+      <c r="T32" t="s">
+        <v>285</v>
       </c>
       <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32" t="s">
-        <v>288</v>
-      </c>
-      <c r="W32">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V32">
+        <v>2</v>
+      </c>
+      <c r="W32" t="s">
+        <v>296</v>
       </c>
       <c r="X32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>330</v>
+        <v>1</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>338</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1610108232</v>
       </c>
       <c r="AE32" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF32">
-        <v>1610108232</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="33" spans="1:34">
+    <row r="33" spans="1:32">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D33">
         <v>8</v>
@@ -4703,40 +4502,40 @@
         <v>1000000</v>
       </c>
       <c r="F33">
-        <v>28500</v>
+        <v>10500</v>
       </c>
       <c r="G33">
-        <v>971500</v>
+        <v>989500</v>
       </c>
       <c r="H33" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I33" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J33" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K33" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L33" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M33">
         <v>3631400</v>
       </c>
       <c r="N33" t="s">
-        <v>255</v>
-      </c>
-      <c r="O33" t="s">
-        <v>82</v>
+        <v>253</v>
+      </c>
+      <c r="O33">
+        <v>989500</v>
       </c>
       <c r="P33">
-        <v>993000</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>993000</v>
+        <v>0</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -4744,58 +4543,52 @@
       <c r="S33">
         <v>0</v>
       </c>
-      <c r="T33">
-        <v>0</v>
+      <c r="T33" t="s">
+        <v>286</v>
       </c>
       <c r="U33">
-        <v>0</v>
-      </c>
-      <c r="V33" t="s">
-        <v>289</v>
-      </c>
-      <c r="W33">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V33">
+        <v>2</v>
+      </c>
+      <c r="W33" t="s">
+        <v>296</v>
       </c>
       <c r="X33">
         <v>2</v>
       </c>
       <c r="Y33" t="s">
-        <v>299</v>
+        <v>328</v>
       </c>
       <c r="Z33">
-        <v>2</v>
-      </c>
-      <c r="AA33" t="s">
-        <v>331</v>
+        <v>1</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>1</v>
-      </c>
-      <c r="AC33">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>338</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>16109012260</v>
       </c>
       <c r="AE33" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF33">
-        <v>16109012260</v>
-      </c>
-      <c r="AG33" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="34" spans="1:34">
+    <row r="34" spans="1:32">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D34">
         <v>11</v>
@@ -4804,102 +4597,96 @@
         <v>1842000</v>
       </c>
       <c r="F34">
-        <v>39603</v>
+        <v>6447</v>
       </c>
       <c r="G34">
-        <v>1802397</v>
+        <v>1835553</v>
       </c>
       <c r="H34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I34" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J34" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K34" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L34" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M34">
         <v>5568200</v>
       </c>
       <c r="N34" t="s">
-        <v>253</v>
-      </c>
-      <c r="O34" t="s">
-        <v>83</v>
+        <v>251</v>
+      </c>
+      <c r="O34">
+        <v>569021</v>
       </c>
       <c r="P34">
-        <v>1835553</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>569021</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1266532</v>
       </c>
       <c r="S34">
         <v>0</v>
       </c>
-      <c r="T34">
-        <v>1266532</v>
+      <c r="T34" t="s">
+        <v>287</v>
       </c>
       <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34" t="s">
-        <v>290</v>
-      </c>
-      <c r="W34">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V34">
+        <v>1</v>
+      </c>
+      <c r="W34" t="s">
+        <v>76</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s">
-        <v>78</v>
+        <v>329</v>
       </c>
       <c r="Z34">
-        <v>20</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>332</v>
+        <v>1</v>
+      </c>
+      <c r="AA34">
+        <v>1</v>
       </c>
       <c r="AB34">
         <v>1</v>
       </c>
-      <c r="AC34">
-        <v>1</v>
+      <c r="AC34" t="s">
+        <v>338</v>
       </c>
       <c r="AD34">
-        <v>1</v>
+        <v>1610104362</v>
       </c>
       <c r="AE34" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF34">
-        <v>1610104362</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH34">
         <v>81081</v>
       </c>
     </row>
-    <row r="35" spans="1:34">
+    <row r="35" spans="1:32">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D35">
         <v>8</v>
@@ -4908,40 +4695,40 @@
         <v>1000000</v>
       </c>
       <c r="F35">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>996500</v>
+        <v>1000000</v>
       </c>
       <c r="H35" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I35" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J35" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="K35" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M35">
         <v>4144500</v>
       </c>
       <c r="N35" t="s">
-        <v>253</v>
-      </c>
-      <c r="O35" t="s">
-        <v>82</v>
+        <v>251</v>
+      </c>
+      <c r="O35">
+        <v>1000000</v>
       </c>
       <c r="P35">
-        <v>996500</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>996500</v>
+        <v>0</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -4949,58 +4736,52 @@
       <c r="S35">
         <v>0</v>
       </c>
-      <c r="T35">
-        <v>0</v>
+      <c r="T35" t="s">
+        <v>288</v>
       </c>
       <c r="U35">
-        <v>0</v>
-      </c>
-      <c r="V35" t="s">
-        <v>291</v>
-      </c>
-      <c r="W35">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V35">
+        <v>2</v>
+      </c>
+      <c r="W35" t="s">
+        <v>296</v>
       </c>
       <c r="X35">
         <v>2</v>
       </c>
       <c r="Y35" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="Z35">
-        <v>2</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>333</v>
+        <v>1</v>
+      </c>
+      <c r="AA35">
+        <v>1</v>
       </c>
       <c r="AB35">
         <v>1</v>
       </c>
-      <c r="AC35">
-        <v>1</v>
+      <c r="AC35" t="s">
+        <v>338</v>
       </c>
       <c r="AD35">
-        <v>1</v>
+        <v>1610906183</v>
       </c>
       <c r="AE35" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF35">
-        <v>1610906183</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="36" spans="1:34">
+    <row r="36" spans="1:32">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D36">
         <v>8</v>
@@ -5009,40 +4790,40 @@
         <v>1000000</v>
       </c>
       <c r="F36">
-        <v>147000</v>
+        <v>21000</v>
       </c>
       <c r="G36">
-        <v>853000</v>
+        <v>979000</v>
       </c>
       <c r="H36" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I36" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K36" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L36" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M36">
         <v>3631400</v>
       </c>
       <c r="N36" t="s">
-        <v>254</v>
-      </c>
-      <c r="O36" t="s">
-        <v>82</v>
+        <v>252</v>
+      </c>
+      <c r="O36">
+        <v>979000</v>
       </c>
       <c r="P36">
-        <v>978000</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>978000</v>
+        <v>0</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -5050,58 +4831,52 @@
       <c r="S36">
         <v>0</v>
       </c>
-      <c r="T36">
-        <v>0</v>
+      <c r="T36" t="s">
+        <v>289</v>
       </c>
       <c r="U36">
-        <v>0</v>
-      </c>
-      <c r="V36" t="s">
-        <v>292</v>
-      </c>
-      <c r="W36">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V36">
+        <v>2</v>
+      </c>
+      <c r="W36" t="s">
+        <v>296</v>
       </c>
       <c r="X36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="s">
-        <v>299</v>
+        <v>331</v>
       </c>
       <c r="Z36">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="s">
-        <v>334</v>
+        <v>2</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>2</v>
-      </c>
-      <c r="AC36">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>338</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1440966659</v>
       </c>
       <c r="AE36" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF36">
-        <v>1440966659</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="37" spans="1:34">
+    <row r="37" spans="1:32">
       <c r="A37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D37">
         <v>9</v>
@@ -5116,96 +4891,90 @@
         <v>1614618</v>
       </c>
       <c r="H37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I37" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J37" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K37" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L37" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M37">
         <v>4935500</v>
       </c>
       <c r="N37" t="s">
-        <v>256</v>
-      </c>
-      <c r="O37" t="s">
+        <v>254</v>
+      </c>
+      <c r="O37">
+        <v>661993</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>952625</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37" t="s">
+        <v>290</v>
+      </c>
+      <c r="U37">
+        <v>2</v>
+      </c>
+      <c r="V37">
+        <v>1</v>
+      </c>
+      <c r="W37" t="s">
+        <v>73</v>
+      </c>
+      <c r="X37">
+        <v>16</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z37">
+        <v>1</v>
+      </c>
+      <c r="AA37">
+        <v>1</v>
+      </c>
+      <c r="AB37">
+        <v>2</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD37">
+        <v>1610104840</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>339</v>
+      </c>
+      <c r="AF37">
+        <v>70881</v>
+      </c>
+    </row>
+    <row r="38" spans="1:32">
+      <c r="A38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" t="s">
         <v>80</v>
-      </c>
-      <c r="P37">
-        <v>1620309</v>
-      </c>
-      <c r="Q37">
-        <v>664327</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>955982</v>
-      </c>
-      <c r="U37">
-        <v>0</v>
-      </c>
-      <c r="V37" t="s">
-        <v>293</v>
-      </c>
-      <c r="W37">
-        <v>2</v>
-      </c>
-      <c r="X37">
-        <v>1</v>
-      </c>
-      <c r="Y37" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z37">
-        <v>16</v>
-      </c>
-      <c r="AA37" t="s">
-        <v>335</v>
-      </c>
-      <c r="AB37">
-        <v>1</v>
-      </c>
-      <c r="AC37">
-        <v>1</v>
-      </c>
-      <c r="AD37">
-        <v>2</v>
-      </c>
-      <c r="AE37" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF37">
-        <v>1610104840</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH37">
-        <v>70881</v>
-      </c>
-    </row>
-    <row r="38" spans="1:34">
-      <c r="A38" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" t="s">
-        <v>82</v>
       </c>
       <c r="D38">
         <v>8</v>
@@ -5220,34 +4989,34 @@
         <v>996500</v>
       </c>
       <c r="H38" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I38" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J38" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K38" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L38" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M38">
         <v>4144500</v>
       </c>
       <c r="N38" t="s">
-        <v>253</v>
-      </c>
-      <c r="O38" t="s">
-        <v>82</v>
+        <v>251</v>
+      </c>
+      <c r="O38">
+        <v>996500</v>
       </c>
       <c r="P38">
-        <v>996500</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>996500</v>
+        <v>0</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -5255,58 +5024,52 @@
       <c r="S38">
         <v>0</v>
       </c>
-      <c r="T38">
-        <v>0</v>
+      <c r="T38" t="s">
+        <v>291</v>
       </c>
       <c r="U38">
-        <v>0</v>
-      </c>
-      <c r="V38" t="s">
-        <v>294</v>
-      </c>
-      <c r="W38">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V38">
+        <v>2</v>
+      </c>
+      <c r="W38" t="s">
+        <v>296</v>
       </c>
       <c r="X38">
         <v>2</v>
       </c>
       <c r="Y38" t="s">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="Z38">
-        <v>2</v>
-      </c>
-      <c r="AA38" t="s">
-        <v>336</v>
+        <v>1</v>
+      </c>
+      <c r="AA38">
+        <v>1</v>
       </c>
       <c r="AB38">
         <v>1</v>
       </c>
-      <c r="AC38">
-        <v>1</v>
+      <c r="AC38" t="s">
+        <v>338</v>
       </c>
       <c r="AD38">
-        <v>1</v>
+        <v>1440924881</v>
       </c>
       <c r="AE38" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF38">
-        <v>1440924881</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="39" spans="1:34">
+    <row r="39" spans="1:32">
       <c r="A39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D39">
         <v>11</v>
@@ -5315,102 +5078,96 @@
         <v>4569000</v>
       </c>
       <c r="F39">
-        <v>493452</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>4075548</v>
+        <v>4569000</v>
       </c>
       <c r="H39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I39" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J39" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K39" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L39" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M39">
         <v>5967000</v>
       </c>
       <c r="N39" t="s">
-        <v>256</v>
-      </c>
-      <c r="O39" t="s">
-        <v>86</v>
+        <v>254</v>
+      </c>
+      <c r="O39">
+        <v>3289680</v>
       </c>
       <c r="P39">
-        <v>4569000</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>3289680</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1279320</v>
       </c>
       <c r="S39">
         <v>0</v>
       </c>
-      <c r="T39">
-        <v>1279320</v>
+      <c r="T39" t="s">
+        <v>292</v>
       </c>
       <c r="U39">
-        <v>0</v>
-      </c>
-      <c r="V39" t="s">
-        <v>295</v>
-      </c>
-      <c r="W39">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V39">
+        <v>1</v>
+      </c>
+      <c r="W39" t="s">
+        <v>77</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y39" t="s">
-        <v>79</v>
+        <v>334</v>
       </c>
       <c r="Z39">
-        <v>19</v>
-      </c>
-      <c r="AA39" t="s">
-        <v>337</v>
+        <v>1</v>
+      </c>
+      <c r="AA39">
+        <v>1</v>
       </c>
       <c r="AB39">
-        <v>1</v>
-      </c>
-      <c r="AC39">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>338</v>
       </c>
       <c r="AD39">
-        <v>2</v>
+        <v>1610102485</v>
       </c>
       <c r="AE39" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF39">
-        <v>1610102485</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH39">
         <v>78605</v>
       </c>
     </row>
-    <row r="40" spans="1:34">
+    <row r="40" spans="1:32">
       <c r="A40" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D40">
         <v>9</v>
@@ -5419,99 +5176,93 @@
         <v>1626000</v>
       </c>
       <c r="F40">
-        <v>5691</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>1620309</v>
+        <v>1626000</v>
       </c>
       <c r="H40" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I40" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J40" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K40" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L40" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M40">
         <v>5207400</v>
       </c>
       <c r="N40" t="s">
-        <v>255</v>
-      </c>
-      <c r="O40" t="s">
-        <v>80</v>
+        <v>253</v>
+      </c>
+      <c r="O40">
+        <v>666660</v>
       </c>
       <c r="P40">
-        <v>1626000</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>666660</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>959340</v>
       </c>
       <c r="S40">
         <v>0</v>
       </c>
-      <c r="T40">
-        <v>959340</v>
+      <c r="T40" t="s">
+        <v>293</v>
       </c>
       <c r="U40">
-        <v>0</v>
-      </c>
-      <c r="V40" t="s">
-        <v>296</v>
-      </c>
-      <c r="W40">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V40">
+        <v>1</v>
+      </c>
+      <c r="W40" t="s">
+        <v>73</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="Y40" t="s">
-        <v>75</v>
+        <v>335</v>
       </c>
       <c r="Z40">
-        <v>22</v>
-      </c>
-      <c r="AA40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA40">
+        <v>1</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="s">
         <v>338</v>
       </c>
-      <c r="AB40">
-        <v>1</v>
-      </c>
-      <c r="AC40">
-        <v>1</v>
-      </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1610100141</v>
       </c>
       <c r="AE40" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF40">
-        <v>1610100141</v>
-      </c>
-      <c r="AG40" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="41" spans="1:34">
+    <row r="41" spans="1:32">
       <c r="A41" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" t="s">
         <v>73</v>
       </c>
-      <c r="B41" t="s">
-        <v>75</v>
-      </c>
       <c r="C41" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D41">
         <v>9</v>
@@ -5520,102 +5271,96 @@
         <v>1626000</v>
       </c>
       <c r="F41">
-        <v>69918</v>
+        <v>5691</v>
       </c>
       <c r="G41">
-        <v>1556082</v>
+        <v>1620309</v>
       </c>
       <c r="H41" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I41" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K41" t="s">
+        <v>247</v>
+      </c>
+      <c r="L41" t="s">
         <v>249</v>
-      </c>
-      <c r="L41" t="s">
-        <v>251</v>
       </c>
       <c r="M41">
         <v>4935500</v>
       </c>
       <c r="N41" t="s">
-        <v>256</v>
-      </c>
-      <c r="O41" t="s">
-        <v>80</v>
+        <v>254</v>
+      </c>
+      <c r="O41">
+        <v>664327</v>
       </c>
       <c r="P41">
-        <v>1620309</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>664327</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>955982</v>
       </c>
       <c r="S41">
         <v>0</v>
       </c>
-      <c r="T41">
-        <v>955982</v>
+      <c r="T41" t="s">
+        <v>294</v>
       </c>
       <c r="U41">
-        <v>0</v>
-      </c>
-      <c r="V41" t="s">
-        <v>297</v>
-      </c>
-      <c r="W41">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V41">
+        <v>1</v>
+      </c>
+      <c r="W41" t="s">
+        <v>73</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y41" t="s">
-        <v>75</v>
+        <v>336</v>
       </c>
       <c r="Z41">
-        <v>16</v>
-      </c>
-      <c r="AA41" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA41">
+        <v>1</v>
+      </c>
+      <c r="AB41">
+        <v>2</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD41">
+        <v>1610901665</v>
+      </c>
+      <c r="AE41" t="s">
         <v>339</v>
       </c>
-      <c r="AB41">
-        <v>1</v>
-      </c>
-      <c r="AC41">
-        <v>1</v>
-      </c>
-      <c r="AD41">
-        <v>2</v>
-      </c>
-      <c r="AE41" t="s">
-        <v>341</v>
-      </c>
       <c r="AF41">
-        <v>1610901665</v>
-      </c>
-      <c r="AG41" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH41">
         <v>73880</v>
       </c>
     </row>
-    <row r="42" spans="1:34">
+    <row r="42" spans="1:32">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D42">
         <v>9</v>
@@ -5624,90 +5369,84 @@
         <v>1626000</v>
       </c>
       <c r="F42">
-        <v>5691</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>1620309</v>
+        <v>1626000</v>
       </c>
       <c r="H42" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I42" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J42" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K42" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="L42" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M42">
         <v>4935500</v>
       </c>
       <c r="N42" t="s">
-        <v>256</v>
-      </c>
-      <c r="O42" t="s">
-        <v>80</v>
+        <v>254</v>
+      </c>
+      <c r="O42">
+        <v>666660</v>
       </c>
       <c r="P42">
-        <v>1626000</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>666660</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>959340</v>
       </c>
       <c r="S42">
         <v>0</v>
       </c>
-      <c r="T42">
-        <v>959340</v>
+      <c r="T42" t="s">
+        <v>295</v>
       </c>
       <c r="U42">
-        <v>0</v>
-      </c>
-      <c r="V42" t="s">
-        <v>298</v>
-      </c>
-      <c r="W42">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="V42">
+        <v>1</v>
+      </c>
+      <c r="W42" t="s">
+        <v>73</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y42" t="s">
-        <v>75</v>
+        <v>337</v>
       </c>
       <c r="Z42">
-        <v>16</v>
-      </c>
-      <c r="AA42" t="s">
-        <v>340</v>
+        <v>1</v>
+      </c>
+      <c r="AA42">
+        <v>1</v>
       </c>
       <c r="AB42">
-        <v>1</v>
-      </c>
-      <c r="AC42">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>338</v>
       </c>
       <c r="AD42">
-        <v>2</v>
+        <v>1610104837</v>
       </c>
       <c r="AE42" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF42">
-        <v>1610104837</v>
-      </c>
-      <c r="AG42" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH42">
         <v>70881</v>
       </c>
     </row>

--- a/gabung.xlsx
+++ b/gabung.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="298">
   <si>
     <t>NAMA PEGAWAI</t>
   </si>
@@ -400,18 +400,9 @@
     <t>14-09-1986</t>
   </si>
   <si>
-    <t>10-04-1967</t>
-  </si>
-  <si>
-    <t>17-07-1999</t>
-  </si>
-  <si>
     <t>22-01-1990</t>
   </si>
   <si>
-    <t>24-04-1993</t>
-  </si>
-  <si>
     <t>01-02-1986</t>
   </si>
   <si>
@@ -436,27 +427,15 @@
     <t>25-08-1981</t>
   </si>
   <si>
-    <t>01-07-1989</t>
-  </si>
-  <si>
     <t>18-08-1981</t>
   </si>
   <si>
-    <t>29-09-1989</t>
-  </si>
-  <si>
-    <t>30-06-1995</t>
-  </si>
-  <si>
     <t>26-04-1982</t>
   </si>
   <si>
     <t>30-04-1989</t>
   </si>
   <si>
-    <t>27-06-1986</t>
-  </si>
-  <si>
     <t>27-03-1982</t>
   </si>
   <si>
@@ -472,39 +451,18 @@
     <t>06-07-1979</t>
   </si>
   <si>
-    <t>07-05-1976</t>
-  </si>
-  <si>
-    <t>12-11-1999</t>
-  </si>
-  <si>
     <t>13-11-1986</t>
   </si>
   <si>
     <t>19-02-1979</t>
   </si>
   <si>
-    <t>02-05-1990</t>
-  </si>
-  <si>
-    <t>18-07-1992</t>
-  </si>
-  <si>
     <t>31-08-1976</t>
   </si>
   <si>
-    <t>23-12-1994</t>
-  </si>
-  <si>
-    <t>08-04-1999</t>
-  </si>
-  <si>
     <t>10-12-1981</t>
   </si>
   <si>
-    <t>10-08-1991</t>
-  </si>
-  <si>
     <t>26-08-1977</t>
   </si>
   <si>
@@ -523,18 +481,9 @@
     <t>90.314.259.4-315.000</t>
   </si>
   <si>
-    <t>80.527.615.1-315.000</t>
-  </si>
-  <si>
-    <t>20.202.776.9-304.000</t>
-  </si>
-  <si>
     <t>84.521.517.7-315.000</t>
   </si>
   <si>
-    <t>65.652.407.1-315.000</t>
-  </si>
-  <si>
     <t>46.884.030.1-425.000</t>
   </si>
   <si>
@@ -559,27 +508,15 @@
     <t>97.015.966.1-305.000</t>
   </si>
   <si>
-    <t>39.870.052.6-304.000</t>
-  </si>
-  <si>
     <t>08.456.457.4-315.000</t>
   </si>
   <si>
-    <t>65.306.654.8-315.000</t>
-  </si>
-  <si>
-    <t>20.220.042.4-315.000</t>
-  </si>
-  <si>
     <t>16.009.399.3-315.000</t>
   </si>
   <si>
     <t>70.352.387.8-305.000</t>
   </si>
   <si>
-    <t>66.158.510.9-315.000</t>
-  </si>
-  <si>
     <t>79.287.648.4-315.000</t>
   </si>
   <si>
@@ -595,39 +532,18 @@
     <t>14.664.001.6-304.000</t>
   </si>
   <si>
-    <t>40.412.808.4-315.000</t>
-  </si>
-  <si>
-    <t>99.948.002.3-304.000</t>
-  </si>
-  <si>
     <t>15.941.951.4-304.000</t>
   </si>
   <si>
     <t>69.552.938.8-315.000</t>
   </si>
   <si>
-    <t>84.574.222.0-315.000</t>
-  </si>
-  <si>
-    <t>94.808.446.2-315.000</t>
-  </si>
-  <si>
     <t>47.631.167.5.315.000</t>
   </si>
   <si>
-    <t>65.667.727.5-315.000</t>
-  </si>
-  <si>
-    <t>20.510.513.3-304.000</t>
-  </si>
-  <si>
     <t>69.552.976.8-315.000</t>
   </si>
   <si>
-    <t>63.796.976.7-315.000</t>
-  </si>
-  <si>
     <t>47.631.176.3.315.000</t>
   </si>
   <si>
@@ -646,18 +562,9 @@
     <t>16109001439</t>
   </si>
   <si>
-    <t>1610800075</t>
-  </si>
-  <si>
-    <t>1440966672</t>
-  </si>
-  <si>
     <t>15509001575</t>
   </si>
   <si>
-    <t>16109012254</t>
-  </si>
-  <si>
     <t>16109012278</t>
   </si>
   <si>
@@ -682,27 +589,15 @@
     <t>1460107125</t>
   </si>
   <si>
-    <t>16109000456</t>
-  </si>
-  <si>
     <t>1900900969</t>
   </si>
   <si>
-    <t>1610906064</t>
-  </si>
-  <si>
-    <t>16109000347</t>
-  </si>
-  <si>
     <t>1610901678</t>
   </si>
   <si>
     <t>1610904070</t>
   </si>
   <si>
-    <t>1820903520</t>
-  </si>
-  <si>
     <t>1610105795</t>
   </si>
   <si>
@@ -718,39 +613,18 @@
     <t>1610103820</t>
   </si>
   <si>
-    <t>1610907514</t>
-  </si>
-  <si>
-    <t>1440966655</t>
-  </si>
-  <si>
     <t>1610904107</t>
   </si>
   <si>
     <t>1610100879</t>
   </si>
   <si>
-    <t>1610108232</t>
-  </si>
-  <si>
-    <t>16109012260</t>
-  </si>
-  <si>
     <t>1610104362</t>
   </si>
   <si>
-    <t>1610906183</t>
-  </si>
-  <si>
-    <t>1440966659</t>
-  </si>
-  <si>
     <t>1610104840</t>
   </si>
   <si>
-    <t>1440924881</t>
-  </si>
-  <si>
     <t>1610102485</t>
   </si>
   <si>
@@ -775,10 +649,10 @@
     <t>TK/0</t>
   </si>
   <si>
+    <t>K/2</t>
+  </si>
+  <si>
     <t>K/0</t>
-  </si>
-  <si>
-    <t>K/2</t>
   </si>
   <si>
     <t>1904010504720002</t>
@@ -1521,19 +1395,19 @@
         <v>126</v>
       </c>
       <c r="J2" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="K2" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="L2" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M2">
         <v>5452600</v>
       </c>
       <c r="N2" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="O2">
         <v>666660</v>
@@ -1551,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="U2">
         <v>2</v>
@@ -1566,7 +1440,7 @@
         <v>24</v>
       </c>
       <c r="Y2" t="s">
-        <v>297</v>
+        <v>255</v>
       </c>
       <c r="Z2">
         <v>1</v>
@@ -1578,13 +1452,13 @@
         <v>1</v>
       </c>
       <c r="AC2" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD2">
         <v>1610102532</v>
       </c>
       <c r="AE2" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF2">
         <v>83635</v>
@@ -1619,19 +1493,19 @@
         <v>127</v>
       </c>
       <c r="J3" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="K3" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="L3" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M3">
         <v>3513600</v>
       </c>
       <c r="N3" t="s">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="O3">
         <v>835120</v>
@@ -1649,7 +1523,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1664,7 +1538,7 @@
         <v>6</v>
       </c>
       <c r="Y3" t="s">
-        <v>298</v>
+        <v>256</v>
       </c>
       <c r="Z3">
         <v>2</v>
@@ -1676,13 +1550,13 @@
         <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD3">
         <v>16109001439</v>
       </c>
       <c r="AE3" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -1710,24 +1584,6 @@
       <c r="H4" t="s">
         <v>87</v>
       </c>
-      <c r="I4" t="s">
-        <v>128</v>
-      </c>
-      <c r="J4" t="s">
-        <v>169</v>
-      </c>
-      <c r="K4" t="s">
-        <v>210</v>
-      </c>
-      <c r="L4" t="s">
-        <v>249</v>
-      </c>
-      <c r="M4">
-        <v>4076400</v>
-      </c>
-      <c r="N4" t="s">
-        <v>253</v>
-      </c>
       <c r="O4">
         <v>1100000</v>
       </c>
@@ -1744,40 +1600,40 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
+        <v>215</v>
+      </c>
+      <c r="U4">
+        <v>2</v>
+      </c>
+      <c r="V4">
+        <v>2</v>
+      </c>
+      <c r="W4" t="s">
+        <v>254</v>
+      </c>
+      <c r="X4">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="s">
         <v>257</v>
       </c>
-      <c r="U4">
-        <v>2</v>
-      </c>
-      <c r="V4">
-        <v>2</v>
-      </c>
-      <c r="W4" t="s">
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="s">
         <v>296</v>
-      </c>
-      <c r="X4">
-        <v>2</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z4">
-        <v>1</v>
-      </c>
-      <c r="AA4">
-        <v>1</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>338</v>
       </c>
       <c r="AD4">
         <v>1610800075</v>
       </c>
       <c r="AE4" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -1805,24 +1661,6 @@
       <c r="H5" t="s">
         <v>88</v>
       </c>
-      <c r="I5" t="s">
-        <v>129</v>
-      </c>
-      <c r="J5" t="s">
-        <v>170</v>
-      </c>
-      <c r="K5" t="s">
-        <v>211</v>
-      </c>
-      <c r="L5" t="s">
-        <v>249</v>
-      </c>
-      <c r="M5">
-        <v>3961800</v>
-      </c>
-      <c r="N5" t="s">
-        <v>253</v>
-      </c>
       <c r="O5">
         <v>1000000</v>
       </c>
@@ -1839,40 +1677,40 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
+        <v>216</v>
+      </c>
+      <c r="U5">
+        <v>2</v>
+      </c>
+      <c r="V5">
+        <v>2</v>
+      </c>
+      <c r="W5" t="s">
+        <v>254</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="s">
         <v>258</v>
       </c>
-      <c r="U5">
-        <v>2</v>
-      </c>
-      <c r="V5">
-        <v>2</v>
-      </c>
-      <c r="W5" t="s">
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="s">
         <v>296</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>300</v>
-      </c>
-      <c r="Z5">
-        <v>1</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>338</v>
       </c>
       <c r="AD5">
         <v>1440966672</v>
       </c>
       <c r="AE5" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -1901,22 +1739,22 @@
         <v>89</v>
       </c>
       <c r="I6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J6" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="K6" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="L6" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M6">
         <v>3959700</v>
       </c>
       <c r="N6" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O6">
         <v>835120</v>
@@ -1934,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>259</v>
+        <v>217</v>
       </c>
       <c r="U6">
         <v>2</v>
@@ -1949,7 +1787,7 @@
         <v>6</v>
       </c>
       <c r="Y6" t="s">
-        <v>301</v>
+        <v>259</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -1961,13 +1799,13 @@
         <v>2</v>
       </c>
       <c r="AC6" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD6">
         <v>15509001575</v>
       </c>
       <c r="AE6" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:32">
@@ -1995,24 +1833,6 @@
       <c r="H7" t="s">
         <v>90</v>
       </c>
-      <c r="I7" t="s">
-        <v>131</v>
-      </c>
-      <c r="J7" t="s">
-        <v>172</v>
-      </c>
-      <c r="K7" t="s">
-        <v>213</v>
-      </c>
-      <c r="L7" t="s">
-        <v>249</v>
-      </c>
-      <c r="M7">
-        <v>4144500</v>
-      </c>
-      <c r="N7" t="s">
-        <v>251</v>
-      </c>
       <c r="O7">
         <v>963500</v>
       </c>
@@ -2029,40 +1849,40 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
+        <v>218</v>
+      </c>
+      <c r="U7">
+        <v>2</v>
+      </c>
+      <c r="V7">
+        <v>2</v>
+      </c>
+      <c r="W7" t="s">
+        <v>254</v>
+      </c>
+      <c r="X7">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="s">
         <v>260</v>
       </c>
-      <c r="U7">
-        <v>2</v>
-      </c>
-      <c r="V7">
-        <v>2</v>
-      </c>
-      <c r="W7" t="s">
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="s">
         <v>296</v>
-      </c>
-      <c r="X7">
-        <v>2</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z7">
-        <v>1</v>
-      </c>
-      <c r="AA7">
-        <v>1</v>
-      </c>
-      <c r="AB7">
-        <v>1</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>338</v>
       </c>
       <c r="AD7">
         <v>1610905992</v>
       </c>
       <c r="AE7" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:32">
@@ -2091,22 +1911,22 @@
         <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J8" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="K8" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="L8" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M8">
         <v>4658300</v>
       </c>
       <c r="N8" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O8">
         <v>659660</v>
@@ -2124,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>261</v>
+        <v>219</v>
       </c>
       <c r="U8">
         <v>2</v>
@@ -2139,7 +1959,7 @@
         <v>10</v>
       </c>
       <c r="Y8" t="s">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="Z8">
         <v>1</v>
@@ -2151,13 +1971,13 @@
         <v>2</v>
       </c>
       <c r="AC8" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD8">
         <v>1610905249</v>
       </c>
       <c r="AE8" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF8">
         <v>66618</v>
@@ -2189,22 +2009,22 @@
         <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J9" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="K9" t="s">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="L9" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M9">
         <v>5080700</v>
       </c>
       <c r="N9" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O9">
         <v>664327</v>
@@ -2222,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>262</v>
+        <v>220</v>
       </c>
       <c r="U9">
         <v>2</v>
@@ -2237,7 +2057,7 @@
         <v>16</v>
       </c>
       <c r="Y9" t="s">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="Z9">
         <v>1</v>
@@ -2249,13 +2069,13 @@
         <v>2</v>
       </c>
       <c r="AC9" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD9">
         <v>1610105556</v>
       </c>
       <c r="AE9" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF9">
         <v>76207</v>
@@ -2287,22 +2107,22 @@
         <v>93</v>
       </c>
       <c r="I10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J10" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="K10" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="L10" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M10">
         <v>4658300</v>
       </c>
       <c r="N10" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O10">
         <v>666660</v>
@@ -2320,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="U10">
         <v>2</v>
@@ -2335,7 +2155,7 @@
         <v>12</v>
       </c>
       <c r="Y10" t="s">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="Z10">
         <v>1</v>
@@ -2347,13 +2167,13 @@
         <v>2</v>
       </c>
       <c r="AC10" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD10">
         <v>1610107829</v>
       </c>
       <c r="AE10" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF10">
         <v>67405</v>
@@ -2385,22 +2205,22 @@
         <v>94</v>
       </c>
       <c r="I11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J11" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="K11" t="s">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="L11" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M11">
         <v>5343700</v>
       </c>
       <c r="N11" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O11">
         <v>531334</v>
@@ -2418,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="U11">
         <v>2</v>
@@ -2433,7 +2253,7 @@
         <v>17</v>
       </c>
       <c r="Y11" t="s">
-        <v>306</v>
+        <v>264</v>
       </c>
       <c r="Z11">
         <v>1</v>
@@ -2445,13 +2265,13 @@
         <v>2</v>
       </c>
       <c r="AC11" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD11">
         <v>1610906028</v>
       </c>
       <c r="AE11" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF11">
         <v>76207</v>
@@ -2483,22 +2303,22 @@
         <v>95</v>
       </c>
       <c r="I12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J12" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="K12" t="s">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="L12" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M12">
         <v>4716400</v>
       </c>
       <c r="N12" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="O12">
         <v>666660</v>
@@ -2516,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="s">
-        <v>265</v>
+        <v>223</v>
       </c>
       <c r="U12">
         <v>2</v>
@@ -2531,7 +2351,7 @@
         <v>14</v>
       </c>
       <c r="Y12" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="Z12">
         <v>1</v>
@@ -2543,13 +2363,13 @@
         <v>1</v>
       </c>
       <c r="AC12" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD12">
         <v>1610106971</v>
       </c>
       <c r="AE12" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF12">
         <v>68716</v>
@@ -2581,22 +2401,22 @@
         <v>96</v>
       </c>
       <c r="I13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J13" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="K13" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="L13" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M13">
         <v>5343700</v>
       </c>
       <c r="N13" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O13">
         <v>571020</v>
@@ -2614,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="U13">
         <v>2</v>
@@ -2629,7 +2449,7 @@
         <v>17</v>
       </c>
       <c r="Y13" t="s">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="Z13">
         <v>1</v>
@@ -2641,13 +2461,13 @@
         <v>2</v>
       </c>
       <c r="AC13" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD13">
         <v>1610106580</v>
       </c>
       <c r="AE13" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF13">
         <v>76207</v>
@@ -2679,22 +2499,22 @@
         <v>97</v>
       </c>
       <c r="I14" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J14" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="K14" t="s">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="L14" t="s">
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="M14">
         <v>5821400</v>
       </c>
       <c r="N14" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O14">
         <v>3984120</v>
@@ -2712,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>267</v>
+        <v>225</v>
       </c>
       <c r="U14">
         <v>2</v>
@@ -2727,7 +2547,7 @@
         <v>18</v>
       </c>
       <c r="Y14" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="Z14">
         <v>1</v>
@@ -2739,13 +2559,13 @@
         <v>2</v>
       </c>
       <c r="AC14" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD14">
         <v>1440105481</v>
       </c>
       <c r="AE14" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15" spans="1:32">
@@ -2774,22 +2594,22 @@
         <v>98</v>
       </c>
       <c r="I15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="J15" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="K15" t="s">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="L15" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M15">
         <v>3934500</v>
       </c>
       <c r="N15" t="s">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="O15">
         <v>835120</v>
@@ -2807,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="U15">
         <v>2</v>
@@ -2822,7 +2642,7 @@
         <v>14</v>
       </c>
       <c r="Y15" t="s">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="Z15">
         <v>2</v>
@@ -2834,13 +2654,13 @@
         <v>0</v>
       </c>
       <c r="AC15" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD15">
         <v>1460107125</v>
       </c>
       <c r="AE15" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" spans="1:32">
@@ -2868,24 +2688,6 @@
       <c r="H16" t="s">
         <v>99</v>
       </c>
-      <c r="I16" t="s">
-        <v>140</v>
-      </c>
-      <c r="J16" t="s">
-        <v>181</v>
-      </c>
-      <c r="K16" t="s">
-        <v>222</v>
-      </c>
-      <c r="L16" t="s">
-        <v>249</v>
-      </c>
-      <c r="M16">
-        <v>3631400</v>
-      </c>
-      <c r="N16" t="s">
-        <v>252</v>
-      </c>
       <c r="O16">
         <v>300000</v>
       </c>
@@ -2902,40 +2704,40 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
+        <v>227</v>
+      </c>
+      <c r="U16">
+        <v>2</v>
+      </c>
+      <c r="V16">
+        <v>2</v>
+      </c>
+      <c r="W16" t="s">
+        <v>254</v>
+      </c>
+      <c r="X16">
+        <v>2</v>
+      </c>
+      <c r="Y16" t="s">
         <v>269</v>
       </c>
-      <c r="U16">
-        <v>2</v>
-      </c>
-      <c r="V16">
-        <v>2</v>
-      </c>
-      <c r="W16" t="s">
+      <c r="Z16">
+        <v>2</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="s">
         <v>296</v>
-      </c>
-      <c r="X16">
-        <v>2</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>311</v>
-      </c>
-      <c r="Z16">
-        <v>2</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>338</v>
       </c>
       <c r="AD16">
         <v>16109000456</v>
       </c>
       <c r="AE16" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:32">
@@ -2964,22 +2766,22 @@
         <v>100</v>
       </c>
       <c r="I17" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="J17" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="K17" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M17">
         <v>5499700</v>
       </c>
       <c r="N17" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O17">
         <v>571020</v>
@@ -2997,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="U17">
         <v>2</v>
@@ -3012,7 +2814,7 @@
         <v>20</v>
       </c>
       <c r="Y17" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="Z17">
         <v>1</v>
@@ -3024,13 +2826,13 @@
         <v>2</v>
       </c>
       <c r="AC17" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD17">
         <v>1900900969</v>
       </c>
       <c r="AE17" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF17">
         <v>78605</v>
@@ -3061,24 +2863,6 @@
       <c r="H18" t="s">
         <v>101</v>
       </c>
-      <c r="I18" t="s">
-        <v>142</v>
-      </c>
-      <c r="J18" t="s">
-        <v>183</v>
-      </c>
-      <c r="K18" t="s">
-        <v>224</v>
-      </c>
-      <c r="L18" t="s">
-        <v>249</v>
-      </c>
-      <c r="M18">
-        <v>4212700</v>
-      </c>
-      <c r="N18" t="s">
-        <v>254</v>
-      </c>
       <c r="O18">
         <v>982000</v>
       </c>
@@ -3095,40 +2879,40 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
+        <v>229</v>
+      </c>
+      <c r="U18">
+        <v>2</v>
+      </c>
+      <c r="V18">
+        <v>2</v>
+      </c>
+      <c r="W18" t="s">
+        <v>254</v>
+      </c>
+      <c r="X18">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="s">
         <v>271</v>
       </c>
-      <c r="U18">
-        <v>2</v>
-      </c>
-      <c r="V18">
-        <v>2</v>
-      </c>
-      <c r="W18" t="s">
+      <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
+      <c r="AB18">
+        <v>2</v>
+      </c>
+      <c r="AC18" t="s">
         <v>296</v>
-      </c>
-      <c r="X18">
-        <v>2</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>313</v>
-      </c>
-      <c r="Z18">
-        <v>1</v>
-      </c>
-      <c r="AA18">
-        <v>1</v>
-      </c>
-      <c r="AB18">
-        <v>2</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>338</v>
       </c>
       <c r="AD18">
         <v>1610906064</v>
       </c>
       <c r="AE18" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" spans="1:32">
@@ -3156,24 +2940,6 @@
       <c r="H19" t="s">
         <v>102</v>
       </c>
-      <c r="I19" t="s">
-        <v>143</v>
-      </c>
-      <c r="J19" t="s">
-        <v>184</v>
-      </c>
-      <c r="K19" t="s">
-        <v>225</v>
-      </c>
-      <c r="L19" t="s">
-        <v>249</v>
-      </c>
-      <c r="M19">
-        <v>3631400</v>
-      </c>
-      <c r="N19" t="s">
-        <v>252</v>
-      </c>
       <c r="O19">
         <v>1000000</v>
       </c>
@@ -3190,40 +2956,40 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
+        <v>230</v>
+      </c>
+      <c r="U19">
+        <v>2</v>
+      </c>
+      <c r="V19">
+        <v>2</v>
+      </c>
+      <c r="W19" t="s">
+        <v>254</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="s">
         <v>272</v>
       </c>
-      <c r="U19">
-        <v>2</v>
-      </c>
-      <c r="V19">
-        <v>2</v>
-      </c>
-      <c r="W19" t="s">
+      <c r="Z19">
+        <v>2</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="s">
         <v>296</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>314</v>
-      </c>
-      <c r="Z19">
-        <v>2</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>338</v>
       </c>
       <c r="AD19">
         <v>16109000347</v>
       </c>
       <c r="AE19" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:32">
@@ -3252,22 +3018,22 @@
         <v>103</v>
       </c>
       <c r="I20" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J20" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="K20" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="L20" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M20">
         <v>4773800</v>
       </c>
       <c r="N20" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="O20">
         <v>661993</v>
@@ -3285,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="U20">
         <v>2</v>
@@ -3300,7 +3066,7 @@
         <v>16</v>
       </c>
       <c r="Y20" t="s">
-        <v>315</v>
+        <v>273</v>
       </c>
       <c r="Z20">
         <v>1</v>
@@ -3312,13 +3078,13 @@
         <v>0</v>
       </c>
       <c r="AC20" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD20">
         <v>1610901678</v>
       </c>
       <c r="AE20" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF20">
         <v>73880</v>
@@ -3350,22 +3116,22 @@
         <v>104</v>
       </c>
       <c r="I21" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="J21" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="K21" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="L21" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M21">
         <v>4658300</v>
       </c>
       <c r="N21" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O21">
         <v>666660</v>
@@ -3383,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>274</v>
+        <v>232</v>
       </c>
       <c r="U21">
         <v>2</v>
@@ -3398,7 +3164,7 @@
         <v>12</v>
       </c>
       <c r="Y21" t="s">
-        <v>316</v>
+        <v>274</v>
       </c>
       <c r="Z21">
         <v>1</v>
@@ -3410,13 +3176,13 @@
         <v>2</v>
       </c>
       <c r="AC21" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD21">
         <v>1610904070</v>
       </c>
       <c r="AE21" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF21">
         <v>66618</v>
@@ -3447,24 +3213,6 @@
       <c r="H22" t="s">
         <v>105</v>
       </c>
-      <c r="I22" t="s">
-        <v>146</v>
-      </c>
-      <c r="J22" t="s">
-        <v>187</v>
-      </c>
-      <c r="K22" t="s">
-        <v>228</v>
-      </c>
-      <c r="L22" t="s">
-        <v>249</v>
-      </c>
-      <c r="M22">
-        <v>3735500</v>
-      </c>
-      <c r="N22" t="s">
-        <v>252</v>
-      </c>
       <c r="O22">
         <v>996500</v>
       </c>
@@ -3481,40 +3229,40 @@
         <v>0</v>
       </c>
       <c r="T22" t="s">
+        <v>233</v>
+      </c>
+      <c r="U22">
+        <v>2</v>
+      </c>
+      <c r="V22">
+        <v>2</v>
+      </c>
+      <c r="W22" t="s">
+        <v>254</v>
+      </c>
+      <c r="X22">
+        <v>2</v>
+      </c>
+      <c r="Y22" t="s">
         <v>275</v>
       </c>
-      <c r="U22">
-        <v>2</v>
-      </c>
-      <c r="V22">
-        <v>2</v>
-      </c>
-      <c r="W22" t="s">
+      <c r="Z22">
+        <v>2</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="s">
         <v>296</v>
-      </c>
-      <c r="X22">
-        <v>2</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>317</v>
-      </c>
-      <c r="Z22">
-        <v>2</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>338</v>
       </c>
       <c r="AD22">
         <v>1820903520</v>
       </c>
       <c r="AE22" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -3543,22 +3291,22 @@
         <v>106</v>
       </c>
       <c r="I23" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="J23" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="K23" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="L23" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M23">
         <v>4496900</v>
       </c>
       <c r="N23" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="O23">
         <v>666660</v>
@@ -3576,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="U23">
         <v>2</v>
@@ -3591,7 +3339,7 @@
         <v>16</v>
       </c>
       <c r="Y23" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="Z23">
         <v>1</v>
@@ -3603,13 +3351,13 @@
         <v>0</v>
       </c>
       <c r="AC23" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD23">
         <v>1610105795</v>
       </c>
       <c r="AE23" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF23">
         <v>76207</v>
@@ -3641,22 +3389,22 @@
         <v>107</v>
       </c>
       <c r="I24" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="J24" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="K24" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="L24" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M24">
         <v>5614000</v>
       </c>
       <c r="N24" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="O24">
         <v>664327</v>
@@ -3674,7 +3422,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>277</v>
+        <v>235</v>
       </c>
       <c r="U24">
         <v>2</v>
@@ -3689,7 +3437,7 @@
         <v>26</v>
       </c>
       <c r="Y24" t="s">
-        <v>319</v>
+        <v>277</v>
       </c>
       <c r="Z24">
         <v>1</v>
@@ -3701,13 +3449,13 @@
         <v>1</v>
       </c>
       <c r="AC24" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD24">
         <v>1610101008</v>
       </c>
       <c r="AE24" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF24">
         <v>86270</v>
@@ -3739,22 +3487,22 @@
         <v>108</v>
       </c>
       <c r="I25" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="J25" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="K25" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="L25" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M25">
         <v>4506300</v>
       </c>
       <c r="N25" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="O25">
         <v>666660</v>
@@ -3772,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="U25">
         <v>2</v>
@@ -3787,7 +3535,7 @@
         <v>10</v>
       </c>
       <c r="Y25" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
       <c r="Z25">
         <v>1</v>
@@ -3799,13 +3547,13 @@
         <v>0</v>
       </c>
       <c r="AC25" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD25">
         <v>1610905245</v>
       </c>
       <c r="AE25" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF25">
         <v>66618</v>
@@ -3837,22 +3585,22 @@
         <v>109</v>
       </c>
       <c r="I26" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="J26" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="K26" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="L26" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M26">
         <v>4935500</v>
       </c>
       <c r="N26" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O26">
         <v>666660</v>
@@ -3870,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="s">
-        <v>279</v>
+        <v>237</v>
       </c>
       <c r="U26">
         <v>2</v>
@@ -3885,7 +3633,7 @@
         <v>16</v>
       </c>
       <c r="Y26" t="s">
-        <v>321</v>
+        <v>279</v>
       </c>
       <c r="Z26">
         <v>1</v>
@@ -3897,13 +3645,13 @@
         <v>2</v>
       </c>
       <c r="AC26" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD26">
         <v>1610104975</v>
       </c>
       <c r="AE26" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF26">
         <v>73880</v>
@@ -3935,22 +3683,22 @@
         <v>110</v>
       </c>
       <c r="I27" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="J27" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="K27" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="L27" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M27">
         <v>4352600</v>
       </c>
       <c r="N27" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="O27">
         <v>1973580</v>
@@ -3968,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>280</v>
+        <v>238</v>
       </c>
       <c r="U27">
         <v>3</v>
@@ -3977,13 +3725,13 @@
         <v>1</v>
       </c>
       <c r="W27" t="s">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="X27">
         <v>16</v>
       </c>
       <c r="Y27" t="s">
-        <v>322</v>
+        <v>280</v>
       </c>
       <c r="Z27">
         <v>1</v>
@@ -3995,13 +3743,13 @@
         <v>1</v>
       </c>
       <c r="AC27" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD27">
         <v>1610103820</v>
       </c>
       <c r="AE27" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:32">
@@ -4029,24 +3777,6 @@
       <c r="H28" t="s">
         <v>111</v>
       </c>
-      <c r="I28" t="s">
-        <v>152</v>
-      </c>
-      <c r="J28" t="s">
-        <v>193</v>
-      </c>
-      <c r="K28" t="s">
-        <v>234</v>
-      </c>
-      <c r="L28" t="s">
-        <v>249</v>
-      </c>
-      <c r="M28">
-        <v>4094000</v>
-      </c>
-      <c r="N28" t="s">
-        <v>254</v>
-      </c>
       <c r="O28">
         <v>1000000</v>
       </c>
@@ -4063,40 +3793,40 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
+        <v>239</v>
+      </c>
+      <c r="U28">
+        <v>2</v>
+      </c>
+      <c r="V28">
+        <v>2</v>
+      </c>
+      <c r="W28" t="s">
+        <v>254</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="s">
         <v>281</v>
       </c>
-      <c r="U28">
-        <v>2</v>
-      </c>
-      <c r="V28">
-        <v>2</v>
-      </c>
-      <c r="W28" t="s">
+      <c r="Z28">
+        <v>1</v>
+      </c>
+      <c r="AA28">
+        <v>1</v>
+      </c>
+      <c r="AB28">
+        <v>2</v>
+      </c>
+      <c r="AC28" t="s">
         <v>296</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>323</v>
-      </c>
-      <c r="Z28">
-        <v>1</v>
-      </c>
-      <c r="AA28">
-        <v>1</v>
-      </c>
-      <c r="AB28">
-        <v>2</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>338</v>
       </c>
       <c r="AD28">
         <v>1610907514</v>
       </c>
       <c r="AE28" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:32">
@@ -4124,24 +3854,6 @@
       <c r="H29" t="s">
         <v>112</v>
       </c>
-      <c r="I29" t="s">
-        <v>153</v>
-      </c>
-      <c r="J29" t="s">
-        <v>194</v>
-      </c>
-      <c r="K29" t="s">
-        <v>235</v>
-      </c>
-      <c r="L29" t="s">
-        <v>249</v>
-      </c>
-      <c r="M29">
-        <v>3961800</v>
-      </c>
-      <c r="N29" t="s">
-        <v>253</v>
-      </c>
       <c r="O29">
         <v>1000000</v>
       </c>
@@ -4158,40 +3870,40 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
+        <v>240</v>
+      </c>
+      <c r="U29">
+        <v>2</v>
+      </c>
+      <c r="V29">
+        <v>2</v>
+      </c>
+      <c r="W29" t="s">
+        <v>254</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="s">
         <v>282</v>
       </c>
-      <c r="U29">
-        <v>2</v>
-      </c>
-      <c r="V29">
-        <v>2</v>
-      </c>
-      <c r="W29" t="s">
+      <c r="Z29">
+        <v>2</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="s">
         <v>296</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>324</v>
-      </c>
-      <c r="Z29">
-        <v>2</v>
-      </c>
-      <c r="AA29">
-        <v>0</v>
-      </c>
-      <c r="AB29">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>338</v>
       </c>
       <c r="AD29">
         <v>1440966655</v>
       </c>
       <c r="AE29" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30" spans="1:32">
@@ -4220,22 +3932,22 @@
         <v>113</v>
       </c>
       <c r="I30" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="J30" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="K30" t="s">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="L30" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M30">
         <v>4935500</v>
       </c>
       <c r="N30" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O30">
         <v>664327</v>
@@ -4253,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>283</v>
+        <v>241</v>
       </c>
       <c r="U30">
         <v>2</v>
@@ -4268,7 +3980,7 @@
         <v>16</v>
       </c>
       <c r="Y30" t="s">
-        <v>325</v>
+        <v>283</v>
       </c>
       <c r="Z30">
         <v>1</v>
@@ -4280,13 +3992,13 @@
         <v>2</v>
       </c>
       <c r="AC30" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD30">
         <v>1610106127</v>
       </c>
       <c r="AE30" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF30">
         <v>73880</v>
@@ -4318,22 +4030,22 @@
         <v>114</v>
       </c>
       <c r="I31" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="J31" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="K31" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="L31" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M31">
         <v>4935500</v>
       </c>
       <c r="N31" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O31">
         <v>666660</v>
@@ -4351,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>284</v>
+        <v>242</v>
       </c>
       <c r="U31">
         <v>2</v>
@@ -4366,7 +4078,7 @@
         <v>16</v>
       </c>
       <c r="Y31" t="s">
-        <v>326</v>
+        <v>284</v>
       </c>
       <c r="Z31">
         <v>1</v>
@@ -4378,13 +4090,13 @@
         <v>2</v>
       </c>
       <c r="AC31" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD31">
         <v>1610100879</v>
       </c>
       <c r="AE31" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF31">
         <v>73880</v>
@@ -4415,24 +4127,6 @@
       <c r="H32" t="s">
         <v>115</v>
       </c>
-      <c r="I32" t="s">
-        <v>156</v>
-      </c>
-      <c r="J32" t="s">
-        <v>197</v>
-      </c>
-      <c r="K32" t="s">
-        <v>238</v>
-      </c>
-      <c r="L32" t="s">
-        <v>249</v>
-      </c>
-      <c r="M32">
-        <v>3631400</v>
-      </c>
-      <c r="N32" t="s">
-        <v>253</v>
-      </c>
       <c r="O32">
         <v>996500</v>
       </c>
@@ -4449,40 +4143,40 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
+        <v>243</v>
+      </c>
+      <c r="U32">
+        <v>2</v>
+      </c>
+      <c r="V32">
+        <v>2</v>
+      </c>
+      <c r="W32" t="s">
+        <v>254</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="s">
         <v>285</v>
       </c>
-      <c r="U32">
-        <v>2</v>
-      </c>
-      <c r="V32">
-        <v>2</v>
-      </c>
-      <c r="W32" t="s">
+      <c r="Z32">
+        <v>1</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="s">
         <v>296</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>327</v>
-      </c>
-      <c r="Z32">
-        <v>1</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>338</v>
       </c>
       <c r="AD32">
         <v>1610108232</v>
       </c>
       <c r="AE32" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:32">
@@ -4510,24 +4204,6 @@
       <c r="H33" t="s">
         <v>116</v>
       </c>
-      <c r="I33" t="s">
-        <v>157</v>
-      </c>
-      <c r="J33" t="s">
-        <v>198</v>
-      </c>
-      <c r="K33" t="s">
-        <v>239</v>
-      </c>
-      <c r="L33" t="s">
-        <v>249</v>
-      </c>
-      <c r="M33">
-        <v>3631400</v>
-      </c>
-      <c r="N33" t="s">
-        <v>253</v>
-      </c>
       <c r="O33">
         <v>989500</v>
       </c>
@@ -4544,40 +4220,40 @@
         <v>0</v>
       </c>
       <c r="T33" t="s">
+        <v>244</v>
+      </c>
+      <c r="U33">
+        <v>2</v>
+      </c>
+      <c r="V33">
+        <v>2</v>
+      </c>
+      <c r="W33" t="s">
+        <v>254</v>
+      </c>
+      <c r="X33">
+        <v>2</v>
+      </c>
+      <c r="Y33" t="s">
         <v>286</v>
       </c>
-      <c r="U33">
-        <v>2</v>
-      </c>
-      <c r="V33">
-        <v>2</v>
-      </c>
-      <c r="W33" t="s">
+      <c r="Z33">
+        <v>1</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="s">
         <v>296</v>
-      </c>
-      <c r="X33">
-        <v>2</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>328</v>
-      </c>
-      <c r="Z33">
-        <v>1</v>
-      </c>
-      <c r="AA33">
-        <v>0</v>
-      </c>
-      <c r="AB33">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>338</v>
       </c>
       <c r="AD33">
         <v>16109012260</v>
       </c>
       <c r="AE33" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:32">
@@ -4606,22 +4282,22 @@
         <v>117</v>
       </c>
       <c r="I34" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="J34" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="K34" t="s">
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="L34" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M34">
         <v>5568200</v>
       </c>
       <c r="N34" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="O34">
         <v>569021</v>
@@ -4639,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>287</v>
+        <v>245</v>
       </c>
       <c r="U34">
         <v>2</v>
@@ -4654,7 +4330,7 @@
         <v>20</v>
       </c>
       <c r="Y34" t="s">
-        <v>329</v>
+        <v>287</v>
       </c>
       <c r="Z34">
         <v>1</v>
@@ -4666,13 +4342,13 @@
         <v>1</v>
       </c>
       <c r="AC34" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD34">
         <v>1610104362</v>
       </c>
       <c r="AE34" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF34">
         <v>81081</v>
@@ -4703,24 +4379,6 @@
       <c r="H35" t="s">
         <v>118</v>
       </c>
-      <c r="I35" t="s">
-        <v>159</v>
-      </c>
-      <c r="J35" t="s">
-        <v>200</v>
-      </c>
-      <c r="K35" t="s">
-        <v>241</v>
-      </c>
-      <c r="L35" t="s">
-        <v>249</v>
-      </c>
-      <c r="M35">
-        <v>4144500</v>
-      </c>
-      <c r="N35" t="s">
-        <v>251</v>
-      </c>
       <c r="O35">
         <v>1000000</v>
       </c>
@@ -4737,40 +4395,40 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
+        <v>246</v>
+      </c>
+      <c r="U35">
+        <v>2</v>
+      </c>
+      <c r="V35">
+        <v>2</v>
+      </c>
+      <c r="W35" t="s">
+        <v>254</v>
+      </c>
+      <c r="X35">
+        <v>2</v>
+      </c>
+      <c r="Y35" t="s">
         <v>288</v>
       </c>
-      <c r="U35">
-        <v>2</v>
-      </c>
-      <c r="V35">
-        <v>2</v>
-      </c>
-      <c r="W35" t="s">
+      <c r="Z35">
+        <v>1</v>
+      </c>
+      <c r="AA35">
+        <v>1</v>
+      </c>
+      <c r="AB35">
+        <v>1</v>
+      </c>
+      <c r="AC35" t="s">
         <v>296</v>
-      </c>
-      <c r="X35">
-        <v>2</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>330</v>
-      </c>
-      <c r="Z35">
-        <v>1</v>
-      </c>
-      <c r="AA35">
-        <v>1</v>
-      </c>
-      <c r="AB35">
-        <v>1</v>
-      </c>
-      <c r="AC35" t="s">
-        <v>338</v>
       </c>
       <c r="AD35">
         <v>1610906183</v>
       </c>
       <c r="AE35" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:32">
@@ -4798,24 +4456,6 @@
       <c r="H36" t="s">
         <v>119</v>
       </c>
-      <c r="I36" t="s">
-        <v>160</v>
-      </c>
-      <c r="J36" t="s">
-        <v>201</v>
-      </c>
-      <c r="K36" t="s">
-        <v>242</v>
-      </c>
-      <c r="L36" t="s">
-        <v>249</v>
-      </c>
-      <c r="M36">
-        <v>3631400</v>
-      </c>
-      <c r="N36" t="s">
-        <v>252</v>
-      </c>
       <c r="O36">
         <v>979000</v>
       </c>
@@ -4832,40 +4472,40 @@
         <v>0</v>
       </c>
       <c r="T36" t="s">
+        <v>247</v>
+      </c>
+      <c r="U36">
+        <v>2</v>
+      </c>
+      <c r="V36">
+        <v>2</v>
+      </c>
+      <c r="W36" t="s">
+        <v>254</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="s">
         <v>289</v>
       </c>
-      <c r="U36">
-        <v>2</v>
-      </c>
-      <c r="V36">
-        <v>2</v>
-      </c>
-      <c r="W36" t="s">
+      <c r="Z36">
+        <v>2</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="s">
         <v>296</v>
-      </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>331</v>
-      </c>
-      <c r="Z36">
-        <v>2</v>
-      </c>
-      <c r="AA36">
-        <v>0</v>
-      </c>
-      <c r="AB36">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="s">
-        <v>338</v>
       </c>
       <c r="AD36">
         <v>1440966659</v>
       </c>
       <c r="AE36" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:32">
@@ -4894,22 +4534,22 @@
         <v>120</v>
       </c>
       <c r="I37" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="J37" t="s">
+        <v>175</v>
+      </c>
+      <c r="K37" t="s">
         <v>202</v>
       </c>
-      <c r="K37" t="s">
-        <v>243</v>
-      </c>
       <c r="L37" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M37">
         <v>4935500</v>
       </c>
       <c r="N37" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O37">
         <v>661993</v>
@@ -4927,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>290</v>
+        <v>248</v>
       </c>
       <c r="U37">
         <v>2</v>
@@ -4942,7 +4582,7 @@
         <v>16</v>
       </c>
       <c r="Y37" t="s">
-        <v>332</v>
+        <v>290</v>
       </c>
       <c r="Z37">
         <v>1</v>
@@ -4954,13 +4594,13 @@
         <v>2</v>
       </c>
       <c r="AC37" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD37">
         <v>1610104840</v>
       </c>
       <c r="AE37" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF37">
         <v>70881</v>
@@ -4991,24 +4631,6 @@
       <c r="H38" t="s">
         <v>121</v>
       </c>
-      <c r="I38" t="s">
-        <v>162</v>
-      </c>
-      <c r="J38" t="s">
-        <v>203</v>
-      </c>
-      <c r="K38" t="s">
-        <v>244</v>
-      </c>
-      <c r="L38" t="s">
-        <v>249</v>
-      </c>
-      <c r="M38">
-        <v>4144500</v>
-      </c>
-      <c r="N38" t="s">
-        <v>251</v>
-      </c>
       <c r="O38">
         <v>996500</v>
       </c>
@@ -5025,40 +4647,40 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
+        <v>249</v>
+      </c>
+      <c r="U38">
+        <v>2</v>
+      </c>
+      <c r="V38">
+        <v>2</v>
+      </c>
+      <c r="W38" t="s">
+        <v>254</v>
+      </c>
+      <c r="X38">
+        <v>2</v>
+      </c>
+      <c r="Y38" t="s">
         <v>291</v>
       </c>
-      <c r="U38">
-        <v>2</v>
-      </c>
-      <c r="V38">
-        <v>2</v>
-      </c>
-      <c r="W38" t="s">
+      <c r="Z38">
+        <v>1</v>
+      </c>
+      <c r="AA38">
+        <v>1</v>
+      </c>
+      <c r="AB38">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="s">
         <v>296</v>
-      </c>
-      <c r="X38">
-        <v>2</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>333</v>
-      </c>
-      <c r="Z38">
-        <v>1</v>
-      </c>
-      <c r="AA38">
-        <v>1</v>
-      </c>
-      <c r="AB38">
-        <v>1</v>
-      </c>
-      <c r="AC38" t="s">
-        <v>338</v>
       </c>
       <c r="AD38">
         <v>1440924881</v>
       </c>
       <c r="AE38" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:32">
@@ -5087,22 +4709,22 @@
         <v>122</v>
       </c>
       <c r="I39" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="J39" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="K39" t="s">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="L39" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M39">
         <v>5967000</v>
       </c>
       <c r="N39" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O39">
         <v>3289680</v>
@@ -5120,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="U39">
         <v>2</v>
@@ -5135,7 +4757,7 @@
         <v>19</v>
       </c>
       <c r="Y39" t="s">
-        <v>334</v>
+        <v>292</v>
       </c>
       <c r="Z39">
         <v>1</v>
@@ -5147,13 +4769,13 @@
         <v>2</v>
       </c>
       <c r="AC39" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD39">
         <v>1610102485</v>
       </c>
       <c r="AE39" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF39">
         <v>78605</v>
@@ -5185,22 +4807,22 @@
         <v>123</v>
       </c>
       <c r="I40" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="J40" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="K40" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="L40" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M40">
         <v>5207400</v>
       </c>
       <c r="N40" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="O40">
         <v>666660</v>
@@ -5218,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>293</v>
+        <v>251</v>
       </c>
       <c r="U40">
         <v>2</v>
@@ -5233,7 +4855,7 @@
         <v>22</v>
       </c>
       <c r="Y40" t="s">
-        <v>335</v>
+        <v>293</v>
       </c>
       <c r="Z40">
         <v>1</v>
@@ -5245,13 +4867,13 @@
         <v>0</v>
       </c>
       <c r="AC40" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD40">
         <v>1610100141</v>
       </c>
       <c r="AE40" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="1:32">
@@ -5280,22 +4902,22 @@
         <v>124</v>
       </c>
       <c r="I41" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="J41" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="K41" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="L41" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="M41">
         <v>4935500</v>
       </c>
       <c r="N41" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O41">
         <v>664327</v>
@@ -5313,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="U41">
         <v>2</v>
@@ -5328,7 +4950,7 @@
         <v>16</v>
       </c>
       <c r="Y41" t="s">
-        <v>336</v>
+        <v>294</v>
       </c>
       <c r="Z41">
         <v>1</v>
@@ -5340,13 +4962,13 @@
         <v>2</v>
       </c>
       <c r="AC41" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD41">
         <v>1610901665</v>
       </c>
       <c r="AE41" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF41">
         <v>73880</v>
@@ -5378,22 +5000,22 @@
         <v>125</v>
       </c>
       <c r="I42" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="J42" t="s">
+        <v>179</v>
+      </c>
+      <c r="K42" t="s">
+        <v>206</v>
+      </c>
+      <c r="L42" t="s">
         <v>207</v>
-      </c>
-      <c r="K42" t="s">
-        <v>248</v>
-      </c>
-      <c r="L42" t="s">
-        <v>249</v>
       </c>
       <c r="M42">
         <v>4935500</v>
       </c>
       <c r="N42" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="O42">
         <v>666660</v>
@@ -5411,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="U42">
         <v>2</v>
@@ -5426,7 +5048,7 @@
         <v>16</v>
       </c>
       <c r="Y42" t="s">
-        <v>337</v>
+        <v>295</v>
       </c>
       <c r="Z42">
         <v>1</v>
@@ -5438,13 +5060,13 @@
         <v>2</v>
       </c>
       <c r="AC42" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="AD42">
         <v>1610104837</v>
       </c>
       <c r="AE42" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AF42">
         <v>70881</v>

--- a/gabung.xlsx
+++ b/gabung.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="244">
   <si>
     <t>NAMA PEGAWAI</t>
   </si>
@@ -394,265 +394,103 @@
     <t>198008292009032001</t>
   </si>
   <si>
-    <t>05-04-1972</t>
-  </si>
-  <si>
-    <t>14-09-1986</t>
-  </si>
-  <si>
-    <t>22-01-1990</t>
-  </si>
-  <si>
-    <t>01-02-1986</t>
-  </si>
-  <si>
-    <t>15-03-1981</t>
-  </si>
-  <si>
-    <t>30-09-1988</t>
-  </si>
-  <si>
-    <t>15-10-1984</t>
-  </si>
-  <si>
-    <t>28-12-1986</t>
-  </si>
-  <si>
-    <t>01-09-1981</t>
-  </si>
-  <si>
-    <t>18-06-1974</t>
-  </si>
-  <si>
-    <t>25-08-1981</t>
-  </si>
-  <si>
-    <t>18-08-1981</t>
-  </si>
-  <si>
-    <t>26-04-1982</t>
-  </si>
-  <si>
-    <t>30-04-1989</t>
-  </si>
-  <si>
-    <t>27-03-1982</t>
-  </si>
-  <si>
-    <t>21-07-1968</t>
-  </si>
-  <si>
-    <t>19-03-1988</t>
-  </si>
-  <si>
-    <t>27-02-1985</t>
-  </si>
-  <si>
-    <t>06-07-1979</t>
-  </si>
-  <si>
-    <t>13-11-1986</t>
-  </si>
-  <si>
-    <t>19-02-1979</t>
-  </si>
-  <si>
-    <t>31-08-1976</t>
-  </si>
-  <si>
-    <t>10-12-1981</t>
-  </si>
-  <si>
-    <t>26-08-1977</t>
-  </si>
-  <si>
-    <t>03-09-1970</t>
-  </si>
-  <si>
-    <t>04-05-1975</t>
-  </si>
-  <si>
-    <t>29-08-1980</t>
-  </si>
-  <si>
-    <t>47.631.159.2-315.000</t>
-  </si>
-  <si>
-    <t>90.314.259.4-315.000</t>
-  </si>
-  <si>
-    <t>84.521.517.7-315.000</t>
-  </si>
-  <si>
-    <t>46.884.030.1-425.000</t>
-  </si>
-  <si>
-    <t>14.646.183.5-315.000</t>
-  </si>
-  <si>
-    <t>70.221.218.4-315.000</t>
-  </si>
-  <si>
-    <t>67.981.915.1-304.000</t>
-  </si>
-  <si>
-    <t>15.939.487.3-315.000</t>
-  </si>
-  <si>
-    <t>14.664.020.6.304.000</t>
-  </si>
-  <si>
-    <t>15.309.140.0-304.000</t>
-  </si>
-  <si>
-    <t>97.015.966.1-305.000</t>
-  </si>
-  <si>
-    <t>08.456.457.4-315.000</t>
-  </si>
-  <si>
-    <t>16.009.399.3-315.000</t>
-  </si>
-  <si>
-    <t>70.352.387.8-305.000</t>
-  </si>
-  <si>
-    <t>79.287.648.4-315.000</t>
-  </si>
-  <si>
-    <t>47.942.395.6-315.000</t>
-  </si>
-  <si>
-    <t>70.266.784.1-315.000</t>
-  </si>
-  <si>
-    <t>15.848.509.4-315.000</t>
-  </si>
-  <si>
-    <t>14.664.001.6-304.000</t>
-  </si>
-  <si>
-    <t>15.941.951.4-304.000</t>
-  </si>
-  <si>
-    <t>69.552.938.8-315.000</t>
-  </si>
-  <si>
-    <t>47.631.167.5.315.000</t>
-  </si>
-  <si>
-    <t>69.552.976.8-315.000</t>
-  </si>
-  <si>
-    <t>47.631.176.3.315.000</t>
-  </si>
-  <si>
-    <t>79.287.650.0-315.000</t>
-  </si>
-  <si>
-    <t>16.009.469.4-315.000</t>
-  </si>
-  <si>
-    <t>67.981.807.0-304.000</t>
-  </si>
-  <si>
-    <t>1610102532</t>
-  </si>
-  <si>
-    <t>16109001439</t>
-  </si>
-  <si>
-    <t>15509001575</t>
-  </si>
-  <si>
-    <t>16109012278</t>
-  </si>
-  <si>
-    <t>1610105556</t>
-  </si>
-  <si>
-    <t>1610107829</t>
-  </si>
-  <si>
-    <t>16109012398</t>
-  </si>
-  <si>
-    <t>16109012246</t>
-  </si>
-  <si>
-    <t>1610106580</t>
-  </si>
-  <si>
-    <t>1440105481</t>
-  </si>
-  <si>
-    <t>1460107125</t>
-  </si>
-  <si>
-    <t>1900900969</t>
-  </si>
-  <si>
-    <t>1610901678</t>
-  </si>
-  <si>
-    <t>1610904070</t>
-  </si>
-  <si>
-    <t>1610105795</t>
-  </si>
-  <si>
-    <t>1610101008</t>
-  </si>
-  <si>
-    <t>1610905245</t>
-  </si>
-  <si>
-    <t>1610104975</t>
-  </si>
-  <si>
-    <t>1610103820</t>
-  </si>
-  <si>
-    <t>1610904107</t>
-  </si>
-  <si>
-    <t>1610100879</t>
-  </si>
-  <si>
-    <t>1610104362</t>
-  </si>
-  <si>
-    <t>1610104840</t>
-  </si>
-  <si>
-    <t>1610102485</t>
-  </si>
-  <si>
-    <t>1610100141</t>
-  </si>
-  <si>
-    <t>1610901665</t>
-  </si>
-  <si>
-    <t>1610104837</t>
+    <t>17-07-1999</t>
+  </si>
+  <si>
+    <t>01-07-1989</t>
+  </si>
+  <si>
+    <t>29-09-1989</t>
+  </si>
+  <si>
+    <t>07-05-1976</t>
+  </si>
+  <si>
+    <t>12-11-1999</t>
+  </si>
+  <si>
+    <t>02-05-1990</t>
+  </si>
+  <si>
+    <t>18-07-1992</t>
+  </si>
+  <si>
+    <t>23-12-1994</t>
+  </si>
+  <si>
+    <t>08-04-1999</t>
+  </si>
+  <si>
+    <t>10-08-1991</t>
+  </si>
+  <si>
+    <t>20.202.776.9-304.000</t>
+  </si>
+  <si>
+    <t>39.870.052.6-304.000</t>
+  </si>
+  <si>
+    <t>65.306.654.8-315.000</t>
+  </si>
+  <si>
+    <t>40.412.808.4-315.000</t>
+  </si>
+  <si>
+    <t>99.948.002.3-304.000</t>
+  </si>
+  <si>
+    <t>84.574.222.0-315.000</t>
+  </si>
+  <si>
+    <t>94.808.446.2-315.000</t>
+  </si>
+  <si>
+    <t>65.667.727.5-315.000</t>
+  </si>
+  <si>
+    <t>20.510.513.3-304.000</t>
+  </si>
+  <si>
+    <t>63.796.976.7-315.000</t>
+  </si>
+  <si>
+    <t>1440966672</t>
+  </si>
+  <si>
+    <t>16109000456</t>
+  </si>
+  <si>
+    <t>16109060640000</t>
+  </si>
+  <si>
+    <t>1610907514</t>
+  </si>
+  <si>
+    <t>1440966655</t>
+  </si>
+  <si>
+    <t>1610108232</t>
+  </si>
+  <si>
+    <t>161090122600000</t>
+  </si>
+  <si>
+    <t>16109061830000</t>
+  </si>
+  <si>
+    <t>1440966659</t>
+  </si>
+  <si>
+    <t>14409248810000</t>
   </si>
   <si>
     <t>[ DINAS PENDIDIKAN ] CABDIN PENDIDIKAN WILAYAH I (BANGKA TENGAH)</t>
   </si>
   <si>
-    <t>[ DINAS PENDIDIKAN ] CABDIN PENDIDIKAN WILAYAH III (BANGKA SELATAN)</t>
-  </si>
-  <si>
-    <t>K/1</t>
+    <t>K/0</t>
   </si>
   <si>
     <t>TK/0</t>
-  </si>
-  <si>
-    <t>K/2</t>
-  </si>
-  <si>
-    <t>K/0</t>
   </si>
   <si>
     <t>1904010504720002</t>
@@ -1391,24 +1229,6 @@
       <c r="H2" t="s">
         <v>85</v>
       </c>
-      <c r="I2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K2" t="s">
-        <v>180</v>
-      </c>
-      <c r="L2" t="s">
-        <v>207</v>
-      </c>
-      <c r="M2">
-        <v>5452600</v>
-      </c>
-      <c r="N2" t="s">
-        <v>209</v>
-      </c>
       <c r="O2">
         <v>666660</v>
       </c>
@@ -1425,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>213</v>
+        <v>159</v>
       </c>
       <c r="U2">
         <v>2</v>
@@ -1440,7 +1260,7 @@
         <v>24</v>
       </c>
       <c r="Y2" t="s">
-        <v>255</v>
+        <v>201</v>
       </c>
       <c r="Z2">
         <v>1</v>
@@ -1452,13 +1272,13 @@
         <v>1</v>
       </c>
       <c r="AC2" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD2">
         <v>1610102532</v>
       </c>
       <c r="AE2" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF2">
         <v>83635</v>
@@ -1489,24 +1309,6 @@
       <c r="H3" t="s">
         <v>86</v>
       </c>
-      <c r="I3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J3" t="s">
-        <v>154</v>
-      </c>
-      <c r="K3" t="s">
-        <v>181</v>
-      </c>
-      <c r="L3" t="s">
-        <v>207</v>
-      </c>
-      <c r="M3">
-        <v>3513600</v>
-      </c>
-      <c r="N3" t="s">
-        <v>210</v>
-      </c>
       <c r="O3">
         <v>835120</v>
       </c>
@@ -1523,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>214</v>
+        <v>160</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1538,7 +1340,7 @@
         <v>6</v>
       </c>
       <c r="Y3" t="s">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="Z3">
         <v>2</v>
@@ -1550,13 +1352,13 @@
         <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD3">
         <v>16109001439</v>
       </c>
       <c r="AE3" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -1600,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
-        <v>215</v>
+        <v>161</v>
       </c>
       <c r="U4">
         <v>2</v>
@@ -1609,13 +1411,13 @@
         <v>2</v>
       </c>
       <c r="W4" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X4">
         <v>2</v>
       </c>
       <c r="Y4" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="Z4">
         <v>1</v>
@@ -1627,13 +1429,13 @@
         <v>0</v>
       </c>
       <c r="AC4" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD4">
         <v>1610800075</v>
       </c>
       <c r="AE4" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -1661,6 +1463,24 @@
       <c r="H5" t="s">
         <v>88</v>
       </c>
+      <c r="I5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J5" t="s">
+        <v>136</v>
+      </c>
+      <c r="K5" t="s">
+        <v>146</v>
+      </c>
+      <c r="L5" t="s">
+        <v>156</v>
+      </c>
+      <c r="M5">
+        <v>34794700</v>
+      </c>
+      <c r="N5" t="s">
+        <v>157</v>
+      </c>
       <c r="O5">
         <v>1000000</v>
       </c>
@@ -1677,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="U5">
         <v>2</v>
@@ -1686,13 +1506,13 @@
         <v>2</v>
       </c>
       <c r="W5" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X5">
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>258</v>
+        <v>204</v>
       </c>
       <c r="Z5">
         <v>1</v>
@@ -1704,13 +1524,13 @@
         <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD5">
         <v>1440966672</v>
       </c>
       <c r="AE5" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -1738,24 +1558,6 @@
       <c r="H6" t="s">
         <v>89</v>
       </c>
-      <c r="I6" t="s">
-        <v>128</v>
-      </c>
-      <c r="J6" t="s">
-        <v>155</v>
-      </c>
-      <c r="K6" t="s">
-        <v>182</v>
-      </c>
-      <c r="L6" t="s">
-        <v>207</v>
-      </c>
-      <c r="M6">
-        <v>3959700</v>
-      </c>
-      <c r="N6" t="s">
-        <v>211</v>
-      </c>
       <c r="O6">
         <v>835120</v>
       </c>
@@ -1772,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>217</v>
+        <v>163</v>
       </c>
       <c r="U6">
         <v>2</v>
@@ -1787,7 +1589,7 @@
         <v>6</v>
       </c>
       <c r="Y6" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -1799,13 +1601,13 @@
         <v>2</v>
       </c>
       <c r="AC6" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD6">
         <v>15509001575</v>
       </c>
       <c r="AE6" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:32">
@@ -1849,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="U7">
         <v>2</v>
@@ -1858,13 +1660,13 @@
         <v>2</v>
       </c>
       <c r="W7" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X7">
         <v>2</v>
       </c>
       <c r="Y7" t="s">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="Z7">
         <v>1</v>
@@ -1876,13 +1678,13 @@
         <v>1</v>
       </c>
       <c r="AC7" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD7">
         <v>1610905992</v>
       </c>
       <c r="AE7" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:32">
@@ -1910,24 +1712,6 @@
       <c r="H8" t="s">
         <v>91</v>
       </c>
-      <c r="I8" t="s">
-        <v>129</v>
-      </c>
-      <c r="J8" t="s">
-        <v>156</v>
-      </c>
-      <c r="K8" t="s">
-        <v>183</v>
-      </c>
-      <c r="L8" t="s">
-        <v>207</v>
-      </c>
-      <c r="M8">
-        <v>4658300</v>
-      </c>
-      <c r="N8" t="s">
-        <v>211</v>
-      </c>
       <c r="O8">
         <v>659660</v>
       </c>
@@ -1944,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="U8">
         <v>2</v>
@@ -1959,7 +1743,7 @@
         <v>10</v>
       </c>
       <c r="Y8" t="s">
-        <v>261</v>
+        <v>207</v>
       </c>
       <c r="Z8">
         <v>1</v>
@@ -1971,13 +1755,13 @@
         <v>2</v>
       </c>
       <c r="AC8" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD8">
         <v>1610905249</v>
       </c>
       <c r="AE8" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF8">
         <v>66618</v>
@@ -2008,24 +1792,6 @@
       <c r="H9" t="s">
         <v>92</v>
       </c>
-      <c r="I9" t="s">
-        <v>130</v>
-      </c>
-      <c r="J9" t="s">
-        <v>157</v>
-      </c>
-      <c r="K9" t="s">
-        <v>184</v>
-      </c>
-      <c r="L9" t="s">
-        <v>207</v>
-      </c>
-      <c r="M9">
-        <v>5080700</v>
-      </c>
-      <c r="N9" t="s">
-        <v>211</v>
-      </c>
       <c r="O9">
         <v>664327</v>
       </c>
@@ -2042,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>220</v>
+        <v>166</v>
       </c>
       <c r="U9">
         <v>2</v>
@@ -2057,7 +1823,7 @@
         <v>16</v>
       </c>
       <c r="Y9" t="s">
-        <v>262</v>
+        <v>208</v>
       </c>
       <c r="Z9">
         <v>1</v>
@@ -2069,13 +1835,13 @@
         <v>2</v>
       </c>
       <c r="AC9" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD9">
         <v>1610105556</v>
       </c>
       <c r="AE9" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF9">
         <v>76207</v>
@@ -2106,24 +1872,6 @@
       <c r="H10" t="s">
         <v>93</v>
       </c>
-      <c r="I10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J10" t="s">
-        <v>158</v>
-      </c>
-      <c r="K10" t="s">
-        <v>185</v>
-      </c>
-      <c r="L10" t="s">
-        <v>207</v>
-      </c>
-      <c r="M10">
-        <v>4658300</v>
-      </c>
-      <c r="N10" t="s">
-        <v>211</v>
-      </c>
       <c r="O10">
         <v>666660</v>
       </c>
@@ -2140,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>221</v>
+        <v>167</v>
       </c>
       <c r="U10">
         <v>2</v>
@@ -2155,7 +1903,7 @@
         <v>12</v>
       </c>
       <c r="Y10" t="s">
-        <v>263</v>
+        <v>209</v>
       </c>
       <c r="Z10">
         <v>1</v>
@@ -2167,13 +1915,13 @@
         <v>2</v>
       </c>
       <c r="AC10" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD10">
         <v>1610107829</v>
       </c>
       <c r="AE10" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF10">
         <v>67405</v>
@@ -2204,24 +1952,6 @@
       <c r="H11" t="s">
         <v>94</v>
       </c>
-      <c r="I11" t="s">
-        <v>132</v>
-      </c>
-      <c r="J11" t="s">
-        <v>159</v>
-      </c>
-      <c r="K11" t="s">
-        <v>186</v>
-      </c>
-      <c r="L11" t="s">
-        <v>207</v>
-      </c>
-      <c r="M11">
-        <v>5343700</v>
-      </c>
-      <c r="N11" t="s">
-        <v>211</v>
-      </c>
       <c r="O11">
         <v>531334</v>
       </c>
@@ -2238,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>222</v>
+        <v>168</v>
       </c>
       <c r="U11">
         <v>2</v>
@@ -2253,7 +1983,7 @@
         <v>17</v>
       </c>
       <c r="Y11" t="s">
-        <v>264</v>
+        <v>210</v>
       </c>
       <c r="Z11">
         <v>1</v>
@@ -2265,13 +1995,13 @@
         <v>2</v>
       </c>
       <c r="AC11" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD11">
         <v>1610906028</v>
       </c>
       <c r="AE11" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF11">
         <v>76207</v>
@@ -2302,24 +2032,6 @@
       <c r="H12" t="s">
         <v>95</v>
       </c>
-      <c r="I12" t="s">
-        <v>133</v>
-      </c>
-      <c r="J12" t="s">
-        <v>160</v>
-      </c>
-      <c r="K12" t="s">
-        <v>187</v>
-      </c>
-      <c r="L12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M12">
-        <v>4716400</v>
-      </c>
-      <c r="N12" t="s">
-        <v>209</v>
-      </c>
       <c r="O12">
         <v>666660</v>
       </c>
@@ -2336,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="s">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="U12">
         <v>2</v>
@@ -2351,7 +2063,7 @@
         <v>14</v>
       </c>
       <c r="Y12" t="s">
-        <v>265</v>
+        <v>211</v>
       </c>
       <c r="Z12">
         <v>1</v>
@@ -2363,13 +2075,13 @@
         <v>1</v>
       </c>
       <c r="AC12" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD12">
         <v>1610106971</v>
       </c>
       <c r="AE12" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF12">
         <v>68716</v>
@@ -2400,24 +2112,6 @@
       <c r="H13" t="s">
         <v>96</v>
       </c>
-      <c r="I13" t="s">
-        <v>134</v>
-      </c>
-      <c r="J13" t="s">
-        <v>161</v>
-      </c>
-      <c r="K13" t="s">
-        <v>188</v>
-      </c>
-      <c r="L13" t="s">
-        <v>207</v>
-      </c>
-      <c r="M13">
-        <v>5343700</v>
-      </c>
-      <c r="N13" t="s">
-        <v>211</v>
-      </c>
       <c r="O13">
         <v>571020</v>
       </c>
@@ -2434,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>224</v>
+        <v>170</v>
       </c>
       <c r="U13">
         <v>2</v>
@@ -2449,7 +2143,7 @@
         <v>17</v>
       </c>
       <c r="Y13" t="s">
-        <v>266</v>
+        <v>212</v>
       </c>
       <c r="Z13">
         <v>1</v>
@@ -2461,13 +2155,13 @@
         <v>2</v>
       </c>
       <c r="AC13" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD13">
         <v>1610106580</v>
       </c>
       <c r="AE13" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF13">
         <v>76207</v>
@@ -2498,24 +2192,6 @@
       <c r="H14" t="s">
         <v>97</v>
       </c>
-      <c r="I14" t="s">
-        <v>135</v>
-      </c>
-      <c r="J14" t="s">
-        <v>162</v>
-      </c>
-      <c r="K14" t="s">
-        <v>189</v>
-      </c>
-      <c r="L14" t="s">
-        <v>208</v>
-      </c>
-      <c r="M14">
-        <v>5821400</v>
-      </c>
-      <c r="N14" t="s">
-        <v>211</v>
-      </c>
       <c r="O14">
         <v>3984120</v>
       </c>
@@ -2532,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="U14">
         <v>2</v>
@@ -2547,7 +2223,7 @@
         <v>18</v>
       </c>
       <c r="Y14" t="s">
-        <v>267</v>
+        <v>213</v>
       </c>
       <c r="Z14">
         <v>1</v>
@@ -2559,13 +2235,13 @@
         <v>2</v>
       </c>
       <c r="AC14" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD14">
         <v>1440105481</v>
       </c>
       <c r="AE14" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:32">
@@ -2593,24 +2269,6 @@
       <c r="H15" t="s">
         <v>98</v>
       </c>
-      <c r="I15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J15" t="s">
-        <v>163</v>
-      </c>
-      <c r="K15" t="s">
-        <v>190</v>
-      </c>
-      <c r="L15" t="s">
-        <v>207</v>
-      </c>
-      <c r="M15">
-        <v>3934500</v>
-      </c>
-      <c r="N15" t="s">
-        <v>210</v>
-      </c>
       <c r="O15">
         <v>835120</v>
       </c>
@@ -2627,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>226</v>
+        <v>172</v>
       </c>
       <c r="U15">
         <v>2</v>
@@ -2642,7 +2300,7 @@
         <v>14</v>
       </c>
       <c r="Y15" t="s">
-        <v>268</v>
+        <v>214</v>
       </c>
       <c r="Z15">
         <v>2</v>
@@ -2654,13 +2312,13 @@
         <v>0</v>
       </c>
       <c r="AC15" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD15">
         <v>1460107125</v>
       </c>
       <c r="AE15" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:32">
@@ -2688,6 +2346,24 @@
       <c r="H16" t="s">
         <v>99</v>
       </c>
+      <c r="I16" t="s">
+        <v>127</v>
+      </c>
+      <c r="J16" t="s">
+        <v>137</v>
+      </c>
+      <c r="K16" t="s">
+        <v>147</v>
+      </c>
+      <c r="L16" t="s">
+        <v>156</v>
+      </c>
+      <c r="M16">
+        <v>32068600</v>
+      </c>
+      <c r="N16" t="s">
+        <v>158</v>
+      </c>
       <c r="O16">
         <v>300000</v>
       </c>
@@ -2704,7 +2380,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="U16">
         <v>2</v>
@@ -2713,13 +2389,13 @@
         <v>2</v>
       </c>
       <c r="W16" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X16">
         <v>2</v>
       </c>
       <c r="Y16" t="s">
-        <v>269</v>
+        <v>215</v>
       </c>
       <c r="Z16">
         <v>2</v>
@@ -2731,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="AC16" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD16">
         <v>16109000456</v>
       </c>
       <c r="AE16" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:32">
@@ -2765,24 +2441,6 @@
       <c r="H17" t="s">
         <v>100</v>
       </c>
-      <c r="I17" t="s">
-        <v>137</v>
-      </c>
-      <c r="J17" t="s">
-        <v>164</v>
-      </c>
-      <c r="K17" t="s">
-        <v>191</v>
-      </c>
-      <c r="L17" t="s">
-        <v>207</v>
-      </c>
-      <c r="M17">
-        <v>5499700</v>
-      </c>
-      <c r="N17" t="s">
-        <v>211</v>
-      </c>
       <c r="O17">
         <v>571020</v>
       </c>
@@ -2799,7 +2457,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="U17">
         <v>2</v>
@@ -2814,7 +2472,7 @@
         <v>20</v>
       </c>
       <c r="Y17" t="s">
-        <v>270</v>
+        <v>216</v>
       </c>
       <c r="Z17">
         <v>1</v>
@@ -2826,13 +2484,13 @@
         <v>2</v>
       </c>
       <c r="AC17" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD17">
         <v>1900900969</v>
       </c>
       <c r="AE17" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF17">
         <v>78605</v>
@@ -2863,6 +2521,24 @@
       <c r="H18" t="s">
         <v>101</v>
       </c>
+      <c r="I18" t="s">
+        <v>128</v>
+      </c>
+      <c r="J18" t="s">
+        <v>138</v>
+      </c>
+      <c r="K18" t="s">
+        <v>148</v>
+      </c>
+      <c r="L18" t="s">
+        <v>156</v>
+      </c>
+      <c r="M18">
+        <v>36964100</v>
+      </c>
+      <c r="N18" t="s">
+        <v>157</v>
+      </c>
       <c r="O18">
         <v>982000</v>
       </c>
@@ -2879,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="U18">
         <v>2</v>
@@ -2888,13 +2564,13 @@
         <v>2</v>
       </c>
       <c r="W18" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X18">
         <v>2</v>
       </c>
       <c r="Y18" t="s">
-        <v>271</v>
+        <v>217</v>
       </c>
       <c r="Z18">
         <v>1</v>
@@ -2906,13 +2582,13 @@
         <v>2</v>
       </c>
       <c r="AC18" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD18">
         <v>1610906064</v>
       </c>
       <c r="AE18" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:32">
@@ -2956,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>230</v>
+        <v>176</v>
       </c>
       <c r="U19">
         <v>2</v>
@@ -2965,13 +2641,13 @@
         <v>2</v>
       </c>
       <c r="W19" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X19">
         <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>272</v>
+        <v>218</v>
       </c>
       <c r="Z19">
         <v>2</v>
@@ -2983,13 +2659,13 @@
         <v>0</v>
       </c>
       <c r="AC19" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD19">
         <v>16109000347</v>
       </c>
       <c r="AE19" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:32">
@@ -3017,24 +2693,6 @@
       <c r="H20" t="s">
         <v>103</v>
       </c>
-      <c r="I20" t="s">
-        <v>138</v>
-      </c>
-      <c r="J20" t="s">
-        <v>165</v>
-      </c>
-      <c r="K20" t="s">
-        <v>192</v>
-      </c>
-      <c r="L20" t="s">
-        <v>207</v>
-      </c>
-      <c r="M20">
-        <v>4773800</v>
-      </c>
-      <c r="N20" t="s">
-        <v>212</v>
-      </c>
       <c r="O20">
         <v>661993</v>
       </c>
@@ -3051,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>231</v>
+        <v>177</v>
       </c>
       <c r="U20">
         <v>2</v>
@@ -3066,7 +2724,7 @@
         <v>16</v>
       </c>
       <c r="Y20" t="s">
-        <v>273</v>
+        <v>219</v>
       </c>
       <c r="Z20">
         <v>1</v>
@@ -3078,13 +2736,13 @@
         <v>0</v>
       </c>
       <c r="AC20" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD20">
         <v>1610901678</v>
       </c>
       <c r="AE20" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF20">
         <v>73880</v>
@@ -3115,24 +2773,6 @@
       <c r="H21" t="s">
         <v>104</v>
       </c>
-      <c r="I21" t="s">
-        <v>139</v>
-      </c>
-      <c r="J21" t="s">
-        <v>166</v>
-      </c>
-      <c r="K21" t="s">
-        <v>193</v>
-      </c>
-      <c r="L21" t="s">
-        <v>207</v>
-      </c>
-      <c r="M21">
-        <v>4658300</v>
-      </c>
-      <c r="N21" t="s">
-        <v>211</v>
-      </c>
       <c r="O21">
         <v>666660</v>
       </c>
@@ -3149,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>232</v>
+        <v>178</v>
       </c>
       <c r="U21">
         <v>2</v>
@@ -3164,7 +2804,7 @@
         <v>12</v>
       </c>
       <c r="Y21" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
       <c r="Z21">
         <v>1</v>
@@ -3176,13 +2816,13 @@
         <v>2</v>
       </c>
       <c r="AC21" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD21">
         <v>1610904070</v>
       </c>
       <c r="AE21" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF21">
         <v>66618</v>
@@ -3229,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="s">
-        <v>233</v>
+        <v>179</v>
       </c>
       <c r="U22">
         <v>2</v>
@@ -3238,13 +2878,13 @@
         <v>2</v>
       </c>
       <c r="W22" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X22">
         <v>2</v>
       </c>
       <c r="Y22" t="s">
-        <v>275</v>
+        <v>221</v>
       </c>
       <c r="Z22">
         <v>2</v>
@@ -3256,13 +2896,13 @@
         <v>0</v>
       </c>
       <c r="AC22" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD22">
         <v>1820903520</v>
       </c>
       <c r="AE22" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -3290,24 +2930,6 @@
       <c r="H23" t="s">
         <v>106</v>
       </c>
-      <c r="I23" t="s">
-        <v>140</v>
-      </c>
-      <c r="J23" t="s">
-        <v>167</v>
-      </c>
-      <c r="K23" t="s">
-        <v>194</v>
-      </c>
-      <c r="L23" t="s">
-        <v>207</v>
-      </c>
-      <c r="M23">
-        <v>4496900</v>
-      </c>
-      <c r="N23" t="s">
-        <v>212</v>
-      </c>
       <c r="O23">
         <v>666660</v>
       </c>
@@ -3324,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="U23">
         <v>2</v>
@@ -3339,7 +2961,7 @@
         <v>16</v>
       </c>
       <c r="Y23" t="s">
-        <v>276</v>
+        <v>222</v>
       </c>
       <c r="Z23">
         <v>1</v>
@@ -3351,13 +2973,13 @@
         <v>0</v>
       </c>
       <c r="AC23" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD23">
         <v>1610105795</v>
       </c>
       <c r="AE23" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF23">
         <v>76207</v>
@@ -3388,24 +3010,6 @@
       <c r="H24" t="s">
         <v>107</v>
       </c>
-      <c r="I24" t="s">
-        <v>141</v>
-      </c>
-      <c r="J24" t="s">
-        <v>168</v>
-      </c>
-      <c r="K24" t="s">
-        <v>195</v>
-      </c>
-      <c r="L24" t="s">
-        <v>207</v>
-      </c>
-      <c r="M24">
-        <v>5614000</v>
-      </c>
-      <c r="N24" t="s">
-        <v>209</v>
-      </c>
       <c r="O24">
         <v>664327</v>
       </c>
@@ -3422,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>235</v>
+        <v>181</v>
       </c>
       <c r="U24">
         <v>2</v>
@@ -3437,7 +3041,7 @@
         <v>26</v>
       </c>
       <c r="Y24" t="s">
-        <v>277</v>
+        <v>223</v>
       </c>
       <c r="Z24">
         <v>1</v>
@@ -3449,13 +3053,13 @@
         <v>1</v>
       </c>
       <c r="AC24" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD24">
         <v>1610101008</v>
       </c>
       <c r="AE24" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF24">
         <v>86270</v>
@@ -3486,24 +3090,6 @@
       <c r="H25" t="s">
         <v>108</v>
       </c>
-      <c r="I25" t="s">
-        <v>142</v>
-      </c>
-      <c r="J25" t="s">
-        <v>169</v>
-      </c>
-      <c r="K25" t="s">
-        <v>196</v>
-      </c>
-      <c r="L25" t="s">
-        <v>207</v>
-      </c>
-      <c r="M25">
-        <v>4506300</v>
-      </c>
-      <c r="N25" t="s">
-        <v>212</v>
-      </c>
       <c r="O25">
         <v>666660</v>
       </c>
@@ -3520,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>236</v>
+        <v>182</v>
       </c>
       <c r="U25">
         <v>2</v>
@@ -3535,7 +3121,7 @@
         <v>10</v>
       </c>
       <c r="Y25" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="Z25">
         <v>1</v>
@@ -3547,13 +3133,13 @@
         <v>0</v>
       </c>
       <c r="AC25" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD25">
         <v>1610905245</v>
       </c>
       <c r="AE25" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF25">
         <v>66618</v>
@@ -3584,24 +3170,6 @@
       <c r="H26" t="s">
         <v>109</v>
       </c>
-      <c r="I26" t="s">
-        <v>143</v>
-      </c>
-      <c r="J26" t="s">
-        <v>170</v>
-      </c>
-      <c r="K26" t="s">
-        <v>197</v>
-      </c>
-      <c r="L26" t="s">
-        <v>207</v>
-      </c>
-      <c r="M26">
-        <v>4935500</v>
-      </c>
-      <c r="N26" t="s">
-        <v>211</v>
-      </c>
       <c r="O26">
         <v>666660</v>
       </c>
@@ -3618,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="s">
-        <v>237</v>
+        <v>183</v>
       </c>
       <c r="U26">
         <v>2</v>
@@ -3633,7 +3201,7 @@
         <v>16</v>
       </c>
       <c r="Y26" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="Z26">
         <v>1</v>
@@ -3645,13 +3213,13 @@
         <v>2</v>
       </c>
       <c r="AC26" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD26">
         <v>1610104975</v>
       </c>
       <c r="AE26" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF26">
         <v>73880</v>
@@ -3682,24 +3250,6 @@
       <c r="H27" t="s">
         <v>110</v>
       </c>
-      <c r="I27" t="s">
-        <v>144</v>
-      </c>
-      <c r="J27" t="s">
-        <v>171</v>
-      </c>
-      <c r="K27" t="s">
-        <v>198</v>
-      </c>
-      <c r="L27" t="s">
-        <v>207</v>
-      </c>
-      <c r="M27">
-        <v>4352600</v>
-      </c>
-      <c r="N27" t="s">
-        <v>209</v>
-      </c>
       <c r="O27">
         <v>1973580</v>
       </c>
@@ -3716,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>238</v>
+        <v>184</v>
       </c>
       <c r="U27">
         <v>3</v>
@@ -3725,13 +3275,13 @@
         <v>1</v>
       </c>
       <c r="W27" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X27">
         <v>16</v>
       </c>
       <c r="Y27" t="s">
-        <v>280</v>
+        <v>226</v>
       </c>
       <c r="Z27">
         <v>1</v>
@@ -3743,13 +3293,13 @@
         <v>1</v>
       </c>
       <c r="AC27" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD27">
         <v>1610103820</v>
       </c>
       <c r="AE27" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28" spans="1:32">
@@ -3777,6 +3327,24 @@
       <c r="H28" t="s">
         <v>111</v>
       </c>
+      <c r="I28" t="s">
+        <v>129</v>
+      </c>
+      <c r="J28" t="s">
+        <v>139</v>
+      </c>
+      <c r="K28" t="s">
+        <v>149</v>
+      </c>
+      <c r="L28" t="s">
+        <v>156</v>
+      </c>
+      <c r="M28">
+        <v>35885200</v>
+      </c>
+      <c r="N28" t="s">
+        <v>157</v>
+      </c>
       <c r="O28">
         <v>1000000</v>
       </c>
@@ -3793,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>239</v>
+        <v>185</v>
       </c>
       <c r="U28">
         <v>2</v>
@@ -3802,13 +3370,13 @@
         <v>2</v>
       </c>
       <c r="W28" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X28">
         <v>0</v>
       </c>
       <c r="Y28" t="s">
-        <v>281</v>
+        <v>227</v>
       </c>
       <c r="Z28">
         <v>1</v>
@@ -3820,13 +3388,13 @@
         <v>2</v>
       </c>
       <c r="AC28" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD28">
         <v>1610907514</v>
       </c>
       <c r="AE28" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" spans="1:32">
@@ -3854,6 +3422,24 @@
       <c r="H29" t="s">
         <v>112</v>
       </c>
+      <c r="I29" t="s">
+        <v>130</v>
+      </c>
+      <c r="J29" t="s">
+        <v>140</v>
+      </c>
+      <c r="K29" t="s">
+        <v>150</v>
+      </c>
+      <c r="L29" t="s">
+        <v>156</v>
+      </c>
+      <c r="M29">
+        <v>35339900</v>
+      </c>
+      <c r="N29" t="s">
+        <v>157</v>
+      </c>
       <c r="O29">
         <v>1000000</v>
       </c>
@@ -3870,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>240</v>
+        <v>186</v>
       </c>
       <c r="U29">
         <v>2</v>
@@ -3879,13 +3465,13 @@
         <v>2</v>
       </c>
       <c r="W29" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X29">
         <v>0</v>
       </c>
       <c r="Y29" t="s">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="Z29">
         <v>2</v>
@@ -3897,13 +3483,13 @@
         <v>0</v>
       </c>
       <c r="AC29" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD29">
         <v>1440966655</v>
       </c>
       <c r="AE29" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" spans="1:32">
@@ -3931,24 +3517,6 @@
       <c r="H30" t="s">
         <v>113</v>
       </c>
-      <c r="I30" t="s">
-        <v>145</v>
-      </c>
-      <c r="J30" t="s">
-        <v>172</v>
-      </c>
-      <c r="K30" t="s">
-        <v>199</v>
-      </c>
-      <c r="L30" t="s">
-        <v>207</v>
-      </c>
-      <c r="M30">
-        <v>4935500</v>
-      </c>
-      <c r="N30" t="s">
-        <v>211</v>
-      </c>
       <c r="O30">
         <v>664327</v>
       </c>
@@ -3965,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>241</v>
+        <v>187</v>
       </c>
       <c r="U30">
         <v>2</v>
@@ -3980,7 +3548,7 @@
         <v>16</v>
       </c>
       <c r="Y30" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="Z30">
         <v>1</v>
@@ -3992,13 +3560,13 @@
         <v>2</v>
       </c>
       <c r="AC30" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD30">
         <v>1610106127</v>
       </c>
       <c r="AE30" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF30">
         <v>73880</v>
@@ -4029,24 +3597,6 @@
       <c r="H31" t="s">
         <v>114</v>
       </c>
-      <c r="I31" t="s">
-        <v>146</v>
-      </c>
-      <c r="J31" t="s">
-        <v>173</v>
-      </c>
-      <c r="K31" t="s">
-        <v>200</v>
-      </c>
-      <c r="L31" t="s">
-        <v>207</v>
-      </c>
-      <c r="M31">
-        <v>4935500</v>
-      </c>
-      <c r="N31" t="s">
-        <v>211</v>
-      </c>
       <c r="O31">
         <v>666660</v>
       </c>
@@ -4063,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>242</v>
+        <v>188</v>
       </c>
       <c r="U31">
         <v>2</v>
@@ -4078,7 +3628,7 @@
         <v>16</v>
       </c>
       <c r="Y31" t="s">
-        <v>284</v>
+        <v>230</v>
       </c>
       <c r="Z31">
         <v>1</v>
@@ -4090,13 +3640,13 @@
         <v>2</v>
       </c>
       <c r="AC31" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD31">
         <v>1610100879</v>
       </c>
       <c r="AE31" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF31">
         <v>73880</v>
@@ -4127,6 +3677,24 @@
       <c r="H32" t="s">
         <v>115</v>
       </c>
+      <c r="I32" t="s">
+        <v>131</v>
+      </c>
+      <c r="J32" t="s">
+        <v>141</v>
+      </c>
+      <c r="K32" t="s">
+        <v>151</v>
+      </c>
+      <c r="L32" t="s">
+        <v>156</v>
+      </c>
+      <c r="M32">
+        <v>32068600</v>
+      </c>
+      <c r="N32" t="s">
+        <v>157</v>
+      </c>
       <c r="O32">
         <v>996500</v>
       </c>
@@ -4143,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>243</v>
+        <v>189</v>
       </c>
       <c r="U32">
         <v>2</v>
@@ -4152,13 +3720,13 @@
         <v>2</v>
       </c>
       <c r="W32" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X32">
         <v>0</v>
       </c>
       <c r="Y32" t="s">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="Z32">
         <v>1</v>
@@ -4170,13 +3738,13 @@
         <v>0</v>
       </c>
       <c r="AC32" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD32">
         <v>1610108232</v>
       </c>
       <c r="AE32" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" spans="1:32">
@@ -4204,6 +3772,24 @@
       <c r="H33" t="s">
         <v>116</v>
       </c>
+      <c r="I33" t="s">
+        <v>132</v>
+      </c>
+      <c r="J33" t="s">
+        <v>142</v>
+      </c>
+      <c r="K33" t="s">
+        <v>152</v>
+      </c>
+      <c r="L33" t="s">
+        <v>156</v>
+      </c>
+      <c r="M33">
+        <v>32068600</v>
+      </c>
+      <c r="N33" t="s">
+        <v>157</v>
+      </c>
       <c r="O33">
         <v>989500</v>
       </c>
@@ -4220,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>244</v>
+        <v>190</v>
       </c>
       <c r="U33">
         <v>2</v>
@@ -4229,13 +3815,13 @@
         <v>2</v>
       </c>
       <c r="W33" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X33">
         <v>2</v>
       </c>
       <c r="Y33" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="Z33">
         <v>1</v>
@@ -4247,13 +3833,13 @@
         <v>0</v>
       </c>
       <c r="AC33" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD33">
         <v>16109012260</v>
       </c>
       <c r="AE33" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:32">
@@ -4281,24 +3867,6 @@
       <c r="H34" t="s">
         <v>117</v>
       </c>
-      <c r="I34" t="s">
-        <v>147</v>
-      </c>
-      <c r="J34" t="s">
-        <v>174</v>
-      </c>
-      <c r="K34" t="s">
-        <v>201</v>
-      </c>
-      <c r="L34" t="s">
-        <v>207</v>
-      </c>
-      <c r="M34">
-        <v>5568200</v>
-      </c>
-      <c r="N34" t="s">
-        <v>209</v>
-      </c>
       <c r="O34">
         <v>569021</v>
       </c>
@@ -4315,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>245</v>
+        <v>191</v>
       </c>
       <c r="U34">
         <v>2</v>
@@ -4330,7 +3898,7 @@
         <v>20</v>
       </c>
       <c r="Y34" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="Z34">
         <v>1</v>
@@ -4342,13 +3910,13 @@
         <v>1</v>
       </c>
       <c r="AC34" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD34">
         <v>1610104362</v>
       </c>
       <c r="AE34" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF34">
         <v>81081</v>
@@ -4379,6 +3947,24 @@
       <c r="H35" t="s">
         <v>118</v>
       </c>
+      <c r="I35" t="s">
+        <v>133</v>
+      </c>
+      <c r="J35" t="s">
+        <v>143</v>
+      </c>
+      <c r="K35" t="s">
+        <v>153</v>
+      </c>
+      <c r="L35" t="s">
+        <v>156</v>
+      </c>
+      <c r="M35">
+        <v>36401600</v>
+      </c>
+      <c r="N35" t="s">
+        <v>157</v>
+      </c>
       <c r="O35">
         <v>1000000</v>
       </c>
@@ -4395,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="U35">
         <v>2</v>
@@ -4404,13 +3990,13 @@
         <v>2</v>
       </c>
       <c r="W35" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X35">
         <v>2</v>
       </c>
       <c r="Y35" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="Z35">
         <v>1</v>
@@ -4422,13 +4008,13 @@
         <v>1</v>
       </c>
       <c r="AC35" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD35">
         <v>1610906183</v>
       </c>
       <c r="AE35" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="36" spans="1:32">
@@ -4456,6 +4042,24 @@
       <c r="H36" t="s">
         <v>119</v>
       </c>
+      <c r="I36" t="s">
+        <v>134</v>
+      </c>
+      <c r="J36" t="s">
+        <v>144</v>
+      </c>
+      <c r="K36" t="s">
+        <v>154</v>
+      </c>
+      <c r="L36" t="s">
+        <v>156</v>
+      </c>
+      <c r="M36">
+        <v>32068600</v>
+      </c>
+      <c r="N36" t="s">
+        <v>158</v>
+      </c>
       <c r="O36">
         <v>979000</v>
       </c>
@@ -4472,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>247</v>
+        <v>193</v>
       </c>
       <c r="U36">
         <v>2</v>
@@ -4481,13 +4085,13 @@
         <v>2</v>
       </c>
       <c r="W36" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X36">
         <v>0</v>
       </c>
       <c r="Y36" t="s">
-        <v>289</v>
+        <v>235</v>
       </c>
       <c r="Z36">
         <v>2</v>
@@ -4499,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="AC36" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD36">
         <v>1440966659</v>
       </c>
       <c r="AE36" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37" spans="1:32">
@@ -4533,24 +4137,6 @@
       <c r="H37" t="s">
         <v>120</v>
       </c>
-      <c r="I37" t="s">
-        <v>148</v>
-      </c>
-      <c r="J37" t="s">
-        <v>175</v>
-      </c>
-      <c r="K37" t="s">
-        <v>202</v>
-      </c>
-      <c r="L37" t="s">
-        <v>207</v>
-      </c>
-      <c r="M37">
-        <v>4935500</v>
-      </c>
-      <c r="N37" t="s">
-        <v>211</v>
-      </c>
       <c r="O37">
         <v>661993</v>
       </c>
@@ -4567,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="U37">
         <v>2</v>
@@ -4582,7 +4168,7 @@
         <v>16</v>
       </c>
       <c r="Y37" t="s">
-        <v>290</v>
+        <v>236</v>
       </c>
       <c r="Z37">
         <v>1</v>
@@ -4594,13 +4180,13 @@
         <v>2</v>
       </c>
       <c r="AC37" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD37">
         <v>1610104840</v>
       </c>
       <c r="AE37" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF37">
         <v>70881</v>
@@ -4631,6 +4217,24 @@
       <c r="H38" t="s">
         <v>121</v>
       </c>
+      <c r="I38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J38" t="s">
+        <v>145</v>
+      </c>
+      <c r="K38" t="s">
+        <v>155</v>
+      </c>
+      <c r="L38" t="s">
+        <v>156</v>
+      </c>
+      <c r="M38">
+        <v>36401600</v>
+      </c>
+      <c r="N38" t="s">
+        <v>157</v>
+      </c>
       <c r="O38">
         <v>996500</v>
       </c>
@@ -4647,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>249</v>
+        <v>195</v>
       </c>
       <c r="U38">
         <v>2</v>
@@ -4656,13 +4260,13 @@
         <v>2</v>
       </c>
       <c r="W38" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="X38">
         <v>2</v>
       </c>
       <c r="Y38" t="s">
-        <v>291</v>
+        <v>237</v>
       </c>
       <c r="Z38">
         <v>1</v>
@@ -4674,13 +4278,13 @@
         <v>1</v>
       </c>
       <c r="AC38" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD38">
         <v>1440924881</v>
       </c>
       <c r="AE38" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="39" spans="1:32">
@@ -4708,24 +4312,6 @@
       <c r="H39" t="s">
         <v>122</v>
       </c>
-      <c r="I39" t="s">
-        <v>149</v>
-      </c>
-      <c r="J39" t="s">
-        <v>176</v>
-      </c>
-      <c r="K39" t="s">
-        <v>203</v>
-      </c>
-      <c r="L39" t="s">
-        <v>207</v>
-      </c>
-      <c r="M39">
-        <v>5967000</v>
-      </c>
-      <c r="N39" t="s">
-        <v>211</v>
-      </c>
       <c r="O39">
         <v>3289680</v>
       </c>
@@ -4742,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>250</v>
+        <v>196</v>
       </c>
       <c r="U39">
         <v>2</v>
@@ -4757,7 +4343,7 @@
         <v>19</v>
       </c>
       <c r="Y39" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="Z39">
         <v>1</v>
@@ -4769,13 +4355,13 @@
         <v>2</v>
       </c>
       <c r="AC39" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD39">
         <v>1610102485</v>
       </c>
       <c r="AE39" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF39">
         <v>78605</v>
@@ -4806,24 +4392,6 @@
       <c r="H40" t="s">
         <v>123</v>
       </c>
-      <c r="I40" t="s">
-        <v>150</v>
-      </c>
-      <c r="J40" t="s">
-        <v>177</v>
-      </c>
-      <c r="K40" t="s">
-        <v>204</v>
-      </c>
-      <c r="L40" t="s">
-        <v>207</v>
-      </c>
-      <c r="M40">
-        <v>5207400</v>
-      </c>
-      <c r="N40" t="s">
-        <v>212</v>
-      </c>
       <c r="O40">
         <v>666660</v>
       </c>
@@ -4840,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>251</v>
+        <v>197</v>
       </c>
       <c r="U40">
         <v>2</v>
@@ -4855,7 +4423,7 @@
         <v>22</v>
       </c>
       <c r="Y40" t="s">
-        <v>293</v>
+        <v>239</v>
       </c>
       <c r="Z40">
         <v>1</v>
@@ -4867,13 +4435,13 @@
         <v>0</v>
       </c>
       <c r="AC40" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD40">
         <v>1610100141</v>
       </c>
       <c r="AE40" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="41" spans="1:32">
@@ -4901,24 +4469,6 @@
       <c r="H41" t="s">
         <v>124</v>
       </c>
-      <c r="I41" t="s">
-        <v>151</v>
-      </c>
-      <c r="J41" t="s">
-        <v>178</v>
-      </c>
-      <c r="K41" t="s">
-        <v>205</v>
-      </c>
-      <c r="L41" t="s">
-        <v>207</v>
-      </c>
-      <c r="M41">
-        <v>4935500</v>
-      </c>
-      <c r="N41" t="s">
-        <v>211</v>
-      </c>
       <c r="O41">
         <v>664327</v>
       </c>
@@ -4935,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>252</v>
+        <v>198</v>
       </c>
       <c r="U41">
         <v>2</v>
@@ -4950,7 +4500,7 @@
         <v>16</v>
       </c>
       <c r="Y41" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="Z41">
         <v>1</v>
@@ -4962,13 +4512,13 @@
         <v>2</v>
       </c>
       <c r="AC41" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD41">
         <v>1610901665</v>
       </c>
       <c r="AE41" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF41">
         <v>73880</v>
@@ -4999,24 +4549,6 @@
       <c r="H42" t="s">
         <v>125</v>
       </c>
-      <c r="I42" t="s">
-        <v>152</v>
-      </c>
-      <c r="J42" t="s">
-        <v>179</v>
-      </c>
-      <c r="K42" t="s">
-        <v>206</v>
-      </c>
-      <c r="L42" t="s">
-        <v>207</v>
-      </c>
-      <c r="M42">
-        <v>4935500</v>
-      </c>
-      <c r="N42" t="s">
-        <v>211</v>
-      </c>
       <c r="O42">
         <v>666660</v>
       </c>
@@ -5033,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>253</v>
+        <v>199</v>
       </c>
       <c r="U42">
         <v>2</v>
@@ -5048,7 +4580,7 @@
         <v>16</v>
       </c>
       <c r="Y42" t="s">
-        <v>295</v>
+        <v>241</v>
       </c>
       <c r="Z42">
         <v>1</v>
@@ -5060,13 +4592,13 @@
         <v>2</v>
       </c>
       <c r="AC42" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="AD42">
         <v>1610104837</v>
       </c>
       <c r="AE42" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="AF42">
         <v>70881</v>

--- a/gabung.xlsx
+++ b/gabung.xlsx
@@ -2860,10 +2860,10 @@
         <v>1000000</v>
       </c>
       <c r="F16">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>300000</v>
+        <v>1000000</v>
       </c>
       <c r="H16" t="s">
         <v>99</v>
@@ -2887,7 +2887,7 @@
         <v>252</v>
       </c>
       <c r="O16">
-        <v>300000</v>
+        <v>1000000</v>
       </c>
       <c r="P16">
         <v>0</v>
